--- a/00_Data/Raw/Wind_Series/Sao Joao do Sabugi.xlsx
+++ b/00_Data/Raw/Wind_Series/Sao Joao do Sabugi.xlsx
@@ -6,21 +6,18 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t xml:space="preserve">Data</t>
+    <t xml:space="preserve">Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Geração</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vento</t>
+    <t xml:space="preserve">Wind_speed</t>
   </si>
 </sst>
 </file>
@@ -364,18 +361,12 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>30682</v>
       </c>
       <c r="B2" t="n">
-        <v>0.453481182795699</v>
-      </c>
-      <c r="C2" t="n">
         <v>6.91118279569892</v>
       </c>
     </row>
@@ -384,9 +375,6 @@
         <v>30713</v>
       </c>
       <c r="B3" t="n">
-        <v>0.494797413793103</v>
-      </c>
-      <c r="C3" t="n">
         <v>7.23297844827586</v>
       </c>
     </row>
@@ -395,9 +383,6 @@
         <v>30742</v>
       </c>
       <c r="B4" t="n">
-        <v>0.225900537634409</v>
-      </c>
-      <c r="C4" t="n">
         <v>5.05323924731183</v>
       </c>
     </row>
@@ -406,9 +391,6 @@
         <v>30773</v>
       </c>
       <c r="B5" t="n">
-        <v>0.240451388888889</v>
-      </c>
-      <c r="C5" t="n">
         <v>5.22029305555556</v>
       </c>
     </row>
@@ -417,9 +399,6 @@
         <v>30803</v>
       </c>
       <c r="B6" t="n">
-        <v>0.397326612903226</v>
-      </c>
-      <c r="C6" t="n">
         <v>6.46285080645161</v>
       </c>
     </row>
@@ -428,9 +407,6 @@
         <v>30834</v>
       </c>
       <c r="B7" t="n">
-        <v>0.543716666666667</v>
-      </c>
-      <c r="C7" t="n">
         <v>7.52190277777778</v>
       </c>
     </row>
@@ -439,9 +415,6 @@
         <v>30864</v>
       </c>
       <c r="B8" t="n">
-        <v>0.614154569892473</v>
-      </c>
-      <c r="C8" t="n">
         <v>8.02832930107527</v>
       </c>
     </row>
@@ -450,9 +423,6 @@
         <v>30895</v>
       </c>
       <c r="B9" t="n">
-        <v>0.638837365591398</v>
-      </c>
-      <c r="C9" t="n">
         <v>8.28479301075269</v>
       </c>
     </row>
@@ -461,9 +431,6 @@
         <v>30926</v>
       </c>
       <c r="B10" t="n">
-        <v>0.630140277777778</v>
-      </c>
-      <c r="C10" t="n">
         <v>8.29303333333333</v>
       </c>
     </row>
@@ -472,9 +439,6 @@
         <v>30956</v>
       </c>
       <c r="B11" t="n">
-        <v>0.690399193548387</v>
-      </c>
-      <c r="C11" t="n">
         <v>8.89713978494624</v>
       </c>
     </row>
@@ -483,9 +447,6 @@
         <v>30987</v>
       </c>
       <c r="B12" t="n">
-        <v>0.642868055555556</v>
-      </c>
-      <c r="C12" t="n">
         <v>8.47689305555556</v>
       </c>
     </row>
@@ -494,9 +455,6 @@
         <v>31017</v>
       </c>
       <c r="B13" t="n">
-        <v>0.553252688172043</v>
-      </c>
-      <c r="C13" t="n">
         <v>7.72379301075269</v>
       </c>
     </row>
@@ -505,9 +463,6 @@
         <v>31048</v>
       </c>
       <c r="B14" t="n">
-        <v>0.339254032258064</v>
-      </c>
-      <c r="C14" t="n">
         <v>5.95888306451613</v>
       </c>
     </row>
@@ -516,9 +471,6 @@
         <v>31079</v>
       </c>
       <c r="B15" t="n">
-        <v>0.203794642857143</v>
-      </c>
-      <c r="C15" t="n">
         <v>4.82835416666667</v>
       </c>
     </row>
@@ -527,9 +479,6 @@
         <v>31107</v>
       </c>
       <c r="B16" t="n">
-        <v>0.232537634408602</v>
-      </c>
-      <c r="C16" t="n">
         <v>5.09667741935484</v>
       </c>
     </row>
@@ -538,9 +487,6 @@
         <v>31138</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1454</v>
-      </c>
-      <c r="C17" t="n">
         <v>4.11080555555556</v>
       </c>
     </row>
@@ -549,9 +495,6 @@
         <v>31168</v>
       </c>
       <c r="B18" t="n">
-        <v>0.393551075268817</v>
-      </c>
-      <c r="C18" t="n">
         <v>6.43787365591398</v>
       </c>
     </row>
@@ -560,9 +503,6 @@
         <v>31199</v>
       </c>
       <c r="B19" t="n">
-        <v>0.407798611111111</v>
-      </c>
-      <c r="C19" t="n">
         <v>6.45683888888889</v>
       </c>
     </row>
@@ -571,9 +511,6 @@
         <v>31229</v>
       </c>
       <c r="B20" t="n">
-        <v>0.626662634408602</v>
-      </c>
-      <c r="C20" t="n">
         <v>8.21310349462366</v>
       </c>
     </row>
@@ -582,9 +519,6 @@
         <v>31260</v>
       </c>
       <c r="B21" t="n">
-        <v>0.629153225806452</v>
-      </c>
-      <c r="C21" t="n">
         <v>8.19512903225806</v>
       </c>
     </row>
@@ -593,9 +527,6 @@
         <v>31291</v>
       </c>
       <c r="B22" t="n">
-        <v>0.659776388888889</v>
-      </c>
-      <c r="C22" t="n">
         <v>8.55170555555556</v>
       </c>
     </row>
@@ -604,9 +535,6 @@
         <v>31321</v>
       </c>
       <c r="B23" t="n">
-        <v>0.617477150537634</v>
-      </c>
-      <c r="C23" t="n">
         <v>8.24925672043011</v>
       </c>
     </row>
@@ -615,9 +543,6 @@
         <v>31352</v>
       </c>
       <c r="B24" t="n">
-        <v>0.63250347705146</v>
-      </c>
-      <c r="C24" t="n">
         <v>8.45441029207232</v>
       </c>
     </row>
@@ -626,9 +551,6 @@
         <v>31382</v>
       </c>
       <c r="B25" t="n">
-        <v>0.408450268817204</v>
-      </c>
-      <c r="C25" t="n">
         <v>6.55984274193548</v>
       </c>
     </row>
@@ -637,9 +559,6 @@
         <v>31413</v>
       </c>
       <c r="B26" t="n">
-        <v>0.485568548387097</v>
-      </c>
-      <c r="C26" t="n">
         <v>7.10199059139785</v>
       </c>
     </row>
@@ -648,9 +567,6 @@
         <v>31444</v>
       </c>
       <c r="B27" t="n">
-        <v>0.284188988095238</v>
-      </c>
-      <c r="C27" t="n">
         <v>5.4663005952381</v>
       </c>
     </row>
@@ -659,9 +575,6 @@
         <v>31472</v>
       </c>
       <c r="B28" t="n">
-        <v>0.191505376344086</v>
-      </c>
-      <c r="C28" t="n">
         <v>4.66770564516129</v>
       </c>
     </row>
@@ -670,9 +583,6 @@
         <v>31503</v>
       </c>
       <c r="B29" t="n">
-        <v>0.267195833333333</v>
-      </c>
-      <c r="C29" t="n">
         <v>5.41224722222222</v>
       </c>
     </row>
@@ -681,9 +591,6 @@
         <v>31533</v>
       </c>
       <c r="B30" t="n">
-        <v>0.485591397849462</v>
-      </c>
-      <c r="C30" t="n">
         <v>7.09139247311828</v>
       </c>
     </row>
@@ -692,9 +599,6 @@
         <v>31564</v>
       </c>
       <c r="B31" t="n">
-        <v>0.6069</v>
-      </c>
-      <c r="C31" t="n">
         <v>8.02550138888889</v>
       </c>
     </row>
@@ -703,9 +607,6 @@
         <v>31594</v>
       </c>
       <c r="B32" t="n">
-        <v>0.560610215053763</v>
-      </c>
-      <c r="C32" t="n">
         <v>7.64247849462366</v>
       </c>
     </row>
@@ -714,9 +615,6 @@
         <v>31625</v>
       </c>
       <c r="B33" t="n">
-        <v>0.582213709677419</v>
-      </c>
-      <c r="C33" t="n">
         <v>7.83472446236559</v>
       </c>
     </row>
@@ -725,9 +623,6 @@
         <v>31656</v>
       </c>
       <c r="B34" t="n">
-        <v>0.739009722222222</v>
-      </c>
-      <c r="C34" t="n">
         <v>9.18057083333333</v>
       </c>
     </row>
@@ -736,9 +631,6 @@
         <v>31686</v>
       </c>
       <c r="B35" t="n">
-        <v>0.604632570659489</v>
-      </c>
-      <c r="C35" t="n">
         <v>8.1798263795424</v>
       </c>
     </row>
@@ -747,9 +639,6 @@
         <v>31717</v>
       </c>
       <c r="B36" t="n">
-        <v>0.687329166666667</v>
-      </c>
-      <c r="C36" t="n">
         <v>8.84177222222222</v>
       </c>
     </row>
@@ -758,9 +647,6 @@
         <v>31747</v>
       </c>
       <c r="B37" t="n">
-        <v>0.602653225806452</v>
-      </c>
-      <c r="C37" t="n">
         <v>8.05946370967742</v>
       </c>
     </row>
@@ -769,9 +655,6 @@
         <v>31778</v>
       </c>
       <c r="B38" t="n">
-        <v>0.517590053763441</v>
-      </c>
-      <c r="C38" t="n">
         <v>7.37745698924731</v>
       </c>
     </row>
@@ -780,9 +663,6 @@
         <v>31809</v>
       </c>
       <c r="B39" t="n">
-        <v>0.489035714285714</v>
-      </c>
-      <c r="C39" t="n">
         <v>7.17228720238095</v>
       </c>
     </row>
@@ -791,9 +671,6 @@
         <v>31837</v>
       </c>
       <c r="B40" t="n">
-        <v>0.202560483870968</v>
-      </c>
-      <c r="C40" t="n">
         <v>4.82601747311828</v>
       </c>
     </row>
@@ -802,9 +679,6 @@
         <v>31868</v>
       </c>
       <c r="B41" t="n">
-        <v>0.432218055555556</v>
-      </c>
-      <c r="C41" t="n">
         <v>6.73122638888889</v>
       </c>
     </row>
@@ -813,9 +687,6 @@
         <v>31898</v>
       </c>
       <c r="B42" t="n">
-        <v>0.498595430107527</v>
-      </c>
-      <c r="C42" t="n">
         <v>7.20276612903226</v>
       </c>
     </row>
@@ -824,9 +695,6 @@
         <v>31929</v>
       </c>
       <c r="B43" t="n">
-        <v>0.524248611111111</v>
-      </c>
-      <c r="C43" t="n">
         <v>7.37989027777778</v>
       </c>
     </row>
@@ -835,9 +703,6 @@
         <v>31959</v>
       </c>
       <c r="B44" t="n">
-        <v>0.628490591397849</v>
-      </c>
-      <c r="C44" t="n">
         <v>8.16686827956989</v>
       </c>
     </row>
@@ -846,9 +711,6 @@
         <v>31990</v>
       </c>
       <c r="B45" t="n">
-        <v>0.632233870967742</v>
-      </c>
-      <c r="C45" t="n">
         <v>8.32034677419355</v>
       </c>
     </row>
@@ -857,9 +719,6 @@
         <v>32021</v>
       </c>
       <c r="B46" t="n">
-        <v>0.646326388888889</v>
-      </c>
-      <c r="C46" t="n">
         <v>8.54476111111111</v>
       </c>
     </row>
@@ -868,9 +727,6 @@
         <v>32051</v>
       </c>
       <c r="B47" t="n">
-        <v>0.574769851951548</v>
-      </c>
-      <c r="C47" t="n">
         <v>8.00525706594886</v>
       </c>
     </row>
@@ -879,9 +735,6 @@
         <v>32082</v>
       </c>
       <c r="B48" t="n">
-        <v>0.653195833333333</v>
-      </c>
-      <c r="C48" t="n">
         <v>8.57534027777778</v>
       </c>
     </row>
@@ -890,9 +743,6 @@
         <v>32112</v>
       </c>
       <c r="B49" t="n">
-        <v>0.63147311827957</v>
-      </c>
-      <c r="C49" t="n">
         <v>8.38175</v>
       </c>
     </row>
@@ -901,9 +751,6 @@
         <v>32143</v>
       </c>
       <c r="B50" t="n">
-        <v>0.444233870967742</v>
-      </c>
-      <c r="C50" t="n">
         <v>6.84566129032258</v>
       </c>
     </row>
@@ -912,9 +759,6 @@
         <v>32174</v>
       </c>
       <c r="B51" t="n">
-        <v>0.372897988505747</v>
-      </c>
-      <c r="C51" t="n">
         <v>6.21725143678161</v>
       </c>
     </row>
@@ -923,9 +767,6 @@
         <v>32203</v>
       </c>
       <c r="B52" t="n">
-        <v>0.269930107526882</v>
-      </c>
-      <c r="C52" t="n">
         <v>5.33661559139785</v>
       </c>
     </row>
@@ -934,9 +775,6 @@
         <v>32234</v>
       </c>
       <c r="B53" t="n">
-        <v>0.254193055555556</v>
-      </c>
-      <c r="C53" t="n">
         <v>5.27301666666667</v>
       </c>
     </row>
@@ -945,9 +783,6 @@
         <v>32264</v>
       </c>
       <c r="B54" t="n">
-        <v>0.394704301075269</v>
-      </c>
-      <c r="C54" t="n">
         <v>6.36915188172043</v>
       </c>
     </row>
@@ -956,9 +791,6 @@
         <v>32295</v>
       </c>
       <c r="B55" t="n">
-        <v>0.556695833333333</v>
-      </c>
-      <c r="C55" t="n">
         <v>7.6663</v>
       </c>
     </row>
@@ -967,9 +799,6 @@
         <v>32325</v>
       </c>
       <c r="B56" t="n">
-        <v>0.679337365591398</v>
-      </c>
-      <c r="C56" t="n">
         <v>8.6928252688172</v>
       </c>
     </row>
@@ -978,9 +807,6 @@
         <v>32356</v>
       </c>
       <c r="B57" t="n">
-        <v>0.72920564516129</v>
-      </c>
-      <c r="C57" t="n">
         <v>9.19445295698925</v>
       </c>
     </row>
@@ -989,9 +815,6 @@
         <v>32387</v>
       </c>
       <c r="B58" t="n">
-        <v>0.731181944444444</v>
-      </c>
-      <c r="C58" t="n">
         <v>9.26046805555556</v>
       </c>
     </row>
@@ -1000,9 +823,6 @@
         <v>32417</v>
       </c>
       <c r="B59" t="n">
-        <v>0.647092866756393</v>
-      </c>
-      <c r="C59" t="n">
         <v>8.59652220726783</v>
       </c>
     </row>
@@ -1011,9 +831,6 @@
         <v>32448</v>
       </c>
       <c r="B60" t="n">
-        <v>0.643383333333333</v>
-      </c>
-      <c r="C60" t="n">
         <v>8.5033125</v>
       </c>
     </row>
@@ -1022,9 +839,6 @@
         <v>32478</v>
       </c>
       <c r="B61" t="n">
-        <v>0.448654569892473</v>
-      </c>
-      <c r="C61" t="n">
         <v>6.83313037634409</v>
       </c>
     </row>
@@ -1033,9 +847,6 @@
         <v>32509</v>
       </c>
       <c r="B62" t="n">
-        <v>0.410909946236559</v>
-      </c>
-      <c r="C62" t="n">
         <v>6.58314112903226</v>
       </c>
     </row>
@@ -1044,9 +855,6 @@
         <v>32540</v>
       </c>
       <c r="B63" t="n">
-        <v>0.429409226190476</v>
-      </c>
-      <c r="C63" t="n">
         <v>6.69656547619048</v>
       </c>
     </row>
@@ -1055,9 +863,6 @@
         <v>32568</v>
       </c>
       <c r="B64" t="n">
-        <v>0.293427419354839</v>
-      </c>
-      <c r="C64" t="n">
         <v>5.59317338709677</v>
       </c>
     </row>
@@ -1066,9 +871,6 @@
         <v>32599</v>
       </c>
       <c r="B65" t="n">
-        <v>0.187354166666667</v>
-      </c>
-      <c r="C65" t="n">
         <v>4.74322916666667</v>
       </c>
     </row>
@@ -1077,9 +879,6 @@
         <v>32629</v>
       </c>
       <c r="B66" t="n">
-        <v>0.345834677419355</v>
-      </c>
-      <c r="C66" t="n">
         <v>6.08965994623656</v>
       </c>
     </row>
@@ -1088,9 +887,6 @@
         <v>32660</v>
       </c>
       <c r="B67" t="n">
-        <v>0.440291666666667</v>
-      </c>
-      <c r="C67" t="n">
         <v>6.762475</v>
       </c>
     </row>
@@ -1099,9 +895,6 @@
         <v>32690</v>
       </c>
       <c r="B68" t="n">
-        <v>0.545995967741935</v>
-      </c>
-      <c r="C68" t="n">
         <v>7.5757123655914</v>
       </c>
     </row>
@@ -1110,9 +903,6 @@
         <v>32721</v>
       </c>
       <c r="B69" t="n">
-        <v>0.642381720430108</v>
-      </c>
-      <c r="C69" t="n">
         <v>8.29143010752688</v>
       </c>
     </row>
@@ -1121,9 +911,6 @@
         <v>32752</v>
       </c>
       <c r="B70" t="n">
-        <v>0.607268055555556</v>
-      </c>
-      <c r="C70" t="n">
         <v>8.08369861111111</v>
       </c>
     </row>
@@ -1132,9 +919,6 @@
         <v>32782</v>
       </c>
       <c r="B71" t="n">
-        <v>0.661220726783311</v>
-      </c>
-      <c r="C71" t="n">
         <v>8.67687213997308</v>
       </c>
     </row>
@@ -1143,9 +927,6 @@
         <v>32813</v>
       </c>
       <c r="B72" t="n">
-        <v>0.646951388888889</v>
-      </c>
-      <c r="C72" t="n">
         <v>8.44868055555555</v>
       </c>
     </row>
@@ -1154,9 +935,6 @@
         <v>32843</v>
       </c>
       <c r="B73" t="n">
-        <v>0.449216397849462</v>
-      </c>
-      <c r="C73" t="n">
         <v>6.84852150537634</v>
       </c>
     </row>
@@ -1165,9 +943,6 @@
         <v>32874</v>
       </c>
       <c r="B74" t="n">
-        <v>0.608469086021505</v>
-      </c>
-      <c r="C74" t="n">
         <v>8.08495295698925</v>
       </c>
     </row>
@@ -1176,9 +951,6 @@
         <v>32905</v>
       </c>
       <c r="B75" t="n">
-        <v>0.342876488095238</v>
-      </c>
-      <c r="C75" t="n">
         <v>6.02314136904762</v>
       </c>
     </row>
@@ -1187,9 +959,6 @@
         <v>32933</v>
       </c>
       <c r="B76" t="n">
-        <v>0.455865591397849</v>
-      </c>
-      <c r="C76" t="n">
         <v>6.90293548387097</v>
       </c>
     </row>
@@ -1198,9 +967,6 @@
         <v>32964</v>
       </c>
       <c r="B77" t="n">
-        <v>0.4354625</v>
-      </c>
-      <c r="C77" t="n">
         <v>6.74565833333333</v>
       </c>
     </row>
@@ -1209,9 +975,6 @@
         <v>32994</v>
       </c>
       <c r="B78" t="n">
-        <v>0.43022311827957</v>
-      </c>
-      <c r="C78" t="n">
         <v>6.63536962365591</v>
       </c>
     </row>
@@ -1220,9 +983,6 @@
         <v>33025</v>
       </c>
       <c r="B79" t="n">
-        <v>0.614984722222222</v>
-      </c>
-      <c r="C79" t="n">
         <v>8.07532638888889</v>
       </c>
     </row>
@@ -1231,9 +991,6 @@
         <v>33055</v>
       </c>
       <c r="B80" t="n">
-        <v>0.554412634408602</v>
-      </c>
-      <c r="C80" t="n">
         <v>7.62046908602151</v>
       </c>
     </row>
@@ -1242,9 +999,6 @@
         <v>33086</v>
       </c>
       <c r="B81" t="n">
-        <v>0.681319892473118</v>
-      </c>
-      <c r="C81" t="n">
         <v>8.62595564516129</v>
       </c>
     </row>
@@ -1253,9 +1007,6 @@
         <v>33117</v>
       </c>
       <c r="B82" t="n">
-        <v>0.647384722222222</v>
-      </c>
-      <c r="C82" t="n">
         <v>8.46085277777778</v>
       </c>
     </row>
@@ -1264,9 +1015,6 @@
         <v>33147</v>
       </c>
       <c r="B83" t="n">
-        <v>0.680682368775236</v>
-      </c>
-      <c r="C83" t="n">
         <v>8.78051682368775</v>
       </c>
     </row>
@@ -1275,9 +1023,6 @@
         <v>33178</v>
       </c>
       <c r="B84" t="n">
-        <v>0.633451388888889</v>
-      </c>
-      <c r="C84" t="n">
         <v>8.34331527777778</v>
       </c>
     </row>
@@ -1286,9 +1031,6 @@
         <v>33208</v>
       </c>
       <c r="B85" t="n">
-        <v>0.54619623655914</v>
-      </c>
-      <c r="C85" t="n">
         <v>7.7107997311828</v>
       </c>
     </row>
@@ -1297,9 +1039,6 @@
         <v>33239</v>
       </c>
       <c r="B86" t="n">
-        <v>0.436861559139785</v>
-      </c>
-      <c r="C86" t="n">
         <v>6.77985349462366</v>
       </c>
     </row>
@@ -1308,9 +1047,6 @@
         <v>33270</v>
       </c>
       <c r="B87" t="n">
-        <v>0.338184523809524</v>
-      </c>
-      <c r="C87" t="n">
         <v>5.94186458333333</v>
       </c>
     </row>
@@ -1319,9 +1055,6 @@
         <v>33298</v>
       </c>
       <c r="B88" t="n">
-        <v>0.363463709677419</v>
-      </c>
-      <c r="C88" t="n">
         <v>6.11200806451613</v>
       </c>
     </row>
@@ -1330,9 +1063,6 @@
         <v>33329</v>
       </c>
       <c r="B89" t="n">
-        <v>0.324413888888889</v>
-      </c>
-      <c r="C89" t="n">
         <v>5.84472361111111</v>
       </c>
     </row>
@@ -1341,9 +1071,6 @@
         <v>33359</v>
       </c>
       <c r="B90" t="n">
-        <v>0.465709677419355</v>
-      </c>
-      <c r="C90" t="n">
         <v>6.96041801075269</v>
       </c>
     </row>
@@ -1352,9 +1079,6 @@
         <v>33390</v>
       </c>
       <c r="B91" t="n">
-        <v>0.619286111111111</v>
-      </c>
-      <c r="C91" t="n">
         <v>8.0866875</v>
       </c>
     </row>
@@ -1363,9 +1087,6 @@
         <v>33420</v>
       </c>
       <c r="B92" t="n">
-        <v>0.707166666666667</v>
-      </c>
-      <c r="C92" t="n">
         <v>8.91122983870968</v>
       </c>
     </row>
@@ -1374,9 +1095,6 @@
         <v>33451</v>
       </c>
       <c r="B93" t="n">
-        <v>0.739837365591398</v>
-      </c>
-      <c r="C93" t="n">
         <v>9.21622311827957</v>
       </c>
     </row>
@@ -1385,9 +1103,6 @@
         <v>33482</v>
       </c>
       <c r="B94" t="n">
-        <v>0.661590277777778</v>
-      </c>
-      <c r="C94" t="n">
         <v>8.61335277777778</v>
       </c>
     </row>
@@ -1396,9 +1111,6 @@
         <v>33512</v>
       </c>
       <c r="B95" t="n">
-        <v>0.643850605652759</v>
-      </c>
-      <c r="C95" t="n">
         <v>8.58816150740242</v>
       </c>
     </row>
@@ -1407,9 +1119,6 @@
         <v>33543</v>
       </c>
       <c r="B96" t="n">
-        <v>0.598731944444444</v>
-      </c>
-      <c r="C96" t="n">
         <v>8.10387083333333</v>
       </c>
     </row>
@@ -1418,9 +1127,6 @@
         <v>33573</v>
       </c>
       <c r="B97" t="n">
-        <v>0.559155913978495</v>
-      </c>
-      <c r="C97" t="n">
         <v>7.77418951612903</v>
       </c>
     </row>
@@ -1429,9 +1135,6 @@
         <v>33604</v>
       </c>
       <c r="B98" t="n">
-        <v>0.481032258064516</v>
-      </c>
-      <c r="C98" t="n">
         <v>7.17504435483871</v>
       </c>
     </row>
@@ -1440,9 +1143,6 @@
         <v>33635</v>
       </c>
       <c r="B99" t="n">
-        <v>0.455020114942529</v>
-      </c>
-      <c r="C99" t="n">
         <v>6.89111206896552</v>
       </c>
     </row>
@@ -1451,9 +1151,6 @@
         <v>33664</v>
       </c>
       <c r="B100" t="n">
-        <v>0.493377688172043</v>
-      </c>
-      <c r="C100" t="n">
         <v>7.16404838709677</v>
       </c>
     </row>
@@ -1462,9 +1159,6 @@
         <v>33695</v>
       </c>
       <c r="B101" t="n">
-        <v>0.428386111111111</v>
-      </c>
-      <c r="C101" t="n">
         <v>6.65690277777778</v>
       </c>
     </row>
@@ -1473,9 +1167,6 @@
         <v>33725</v>
       </c>
       <c r="B102" t="n">
-        <v>0.461690860215054</v>
-      </c>
-      <c r="C102" t="n">
         <v>6.94216801075269</v>
       </c>
     </row>
@@ -1484,9 +1175,6 @@
         <v>33756</v>
       </c>
       <c r="B103" t="n">
-        <v>0.554768055555556</v>
-      </c>
-      <c r="C103" t="n">
         <v>7.6109625</v>
       </c>
     </row>
@@ -1495,9 +1183,6 @@
         <v>33786</v>
       </c>
       <c r="B104" t="n">
-        <v>0.605995967741936</v>
-      </c>
-      <c r="C104" t="n">
         <v>8.0230752688172</v>
       </c>
     </row>
@@ -1506,9 +1191,6 @@
         <v>33817</v>
       </c>
       <c r="B105" t="n">
-        <v>0.637345430107527</v>
-      </c>
-      <c r="C105" t="n">
         <v>8.37596370967742</v>
       </c>
     </row>
@@ -1517,9 +1199,6 @@
         <v>33848</v>
       </c>
       <c r="B106" t="n">
-        <v>0.652770833333333</v>
-      </c>
-      <c r="C106" t="n">
         <v>8.56197222222222</v>
       </c>
     </row>
@@ -1528,9 +1207,6 @@
         <v>33878</v>
       </c>
       <c r="B107" t="n">
-        <v>0.664009421265141</v>
-      </c>
-      <c r="C107" t="n">
         <v>8.70262180349933</v>
       </c>
     </row>
@@ -1539,9 +1215,6 @@
         <v>33909</v>
       </c>
       <c r="B108" t="n">
-        <v>0.6333125</v>
-      </c>
-      <c r="C108" t="n">
         <v>8.42195694444444</v>
       </c>
     </row>
@@ -1550,9 +1223,6 @@
         <v>33939</v>
       </c>
       <c r="B109" t="n">
-        <v>0.563095430107527</v>
-      </c>
-      <c r="C109" t="n">
         <v>7.8244811827957</v>
       </c>
     </row>
@@ -1561,9 +1231,6 @@
         <v>33970</v>
       </c>
       <c r="B110" t="n">
-        <v>0.479681451612903</v>
-      </c>
-      <c r="C110" t="n">
         <v>7.08902688172043</v>
       </c>
     </row>
@@ -1572,9 +1239,6 @@
         <v>34001</v>
       </c>
       <c r="B111" t="n">
-        <v>0.431852678571429</v>
-      </c>
-      <c r="C111" t="n">
         <v>6.71447767857143</v>
       </c>
     </row>
@@ -1583,9 +1247,6 @@
         <v>34029</v>
       </c>
       <c r="B112" t="n">
-        <v>0.428815860215054</v>
-      </c>
-      <c r="C112" t="n">
         <v>6.69383602150538</v>
       </c>
     </row>
@@ -1594,9 +1255,6 @@
         <v>34060</v>
       </c>
       <c r="B113" t="n">
-        <v>0.443029166666667</v>
-      </c>
-      <c r="C113" t="n">
         <v>6.77682361111111</v>
       </c>
     </row>
@@ -1605,9 +1263,6 @@
         <v>34090</v>
       </c>
       <c r="B114" t="n">
-        <v>0.527224462365591</v>
-      </c>
-      <c r="C114" t="n">
         <v>7.42858467741936</v>
       </c>
     </row>
@@ -1616,9 +1271,6 @@
         <v>34121</v>
       </c>
       <c r="B115" t="n">
-        <v>0.607708333333333</v>
-      </c>
-      <c r="C115" t="n">
         <v>8.03293611111111</v>
       </c>
     </row>
@@ -1627,9 +1279,6 @@
         <v>34151</v>
       </c>
       <c r="B116" t="n">
-        <v>0.632068548387097</v>
-      </c>
-      <c r="C116" t="n">
         <v>8.22767607526882</v>
       </c>
     </row>
@@ -1638,9 +1287,6 @@
         <v>34182</v>
       </c>
       <c r="B117" t="n">
-        <v>0.617016129032258</v>
-      </c>
-      <c r="C117" t="n">
         <v>8.16865322580645</v>
       </c>
     </row>
@@ -1649,9 +1295,6 @@
         <v>34213</v>
       </c>
       <c r="B118" t="n">
-        <v>0.545381944444444</v>
-      </c>
-      <c r="C118" t="n">
         <v>7.67075972222222</v>
       </c>
     </row>
@@ -1660,9 +1303,6 @@
         <v>34243</v>
       </c>
       <c r="B119" t="n">
-        <v>0.652091520861373</v>
-      </c>
-      <c r="C119" t="n">
         <v>8.60886810228802</v>
       </c>
     </row>
@@ -1671,9 +1311,6 @@
         <v>34274</v>
       </c>
       <c r="B120" t="n">
-        <v>0.660484722222222</v>
-      </c>
-      <c r="C120" t="n">
         <v>8.66212361111111</v>
       </c>
     </row>
@@ -1682,9 +1319,6 @@
         <v>34304</v>
       </c>
       <c r="B121" t="n">
-        <v>0.606813172043011</v>
-      </c>
-      <c r="C121" t="n">
         <v>8.15523655913979</v>
       </c>
     </row>
@@ -1693,9 +1327,6 @@
         <v>34335</v>
       </c>
       <c r="B122" t="n">
-        <v>0.300301075268817</v>
-      </c>
-      <c r="C122" t="n">
         <v>5.66614650537634</v>
       </c>
     </row>
@@ -1704,9 +1335,6 @@
         <v>34366</v>
       </c>
       <c r="B123" t="n">
-        <v>0.325983630952381</v>
-      </c>
-      <c r="C123" t="n">
         <v>5.84497619047619</v>
       </c>
     </row>
@@ -1715,9 +1343,6 @@
         <v>34394</v>
       </c>
       <c r="B124" t="n">
-        <v>0.288072580645161</v>
-      </c>
-      <c r="C124" t="n">
         <v>5.63387903225806</v>
       </c>
     </row>
@@ -1726,9 +1351,6 @@
         <v>34425</v>
       </c>
       <c r="B125" t="n">
-        <v>0.319158333333333</v>
-      </c>
-      <c r="C125" t="n">
         <v>5.80204583333333</v>
       </c>
     </row>
@@ -1737,9 +1359,6 @@
         <v>34455</v>
       </c>
       <c r="B126" t="n">
-        <v>0.443126344086022</v>
-      </c>
-      <c r="C126" t="n">
         <v>6.80705779569892</v>
       </c>
     </row>
@@ -1748,9 +1367,6 @@
         <v>34486</v>
       </c>
       <c r="B127" t="n">
-        <v>0.451818055555556</v>
-      </c>
-      <c r="C127" t="n">
         <v>6.86537083333333</v>
       </c>
     </row>
@@ -1759,9 +1375,6 @@
         <v>34516</v>
       </c>
       <c r="B128" t="n">
-        <v>0.630702956989247</v>
-      </c>
-      <c r="C128" t="n">
         <v>8.17062634408602</v>
       </c>
     </row>
@@ -1770,9 +1383,6 @@
         <v>34547</v>
       </c>
       <c r="B129" t="n">
-        <v>0.668396505376344</v>
-      </c>
-      <c r="C129" t="n">
         <v>8.55242741935484</v>
       </c>
     </row>
@@ -1781,9 +1391,6 @@
         <v>34578</v>
       </c>
       <c r="B130" t="n">
-        <v>0.708670833333333</v>
-      </c>
-      <c r="C130" t="n">
         <v>9.01254861111111</v>
       </c>
     </row>
@@ -1792,9 +1399,6 @@
         <v>34608</v>
       </c>
       <c r="B131" t="n">
-        <v>0.662590847913863</v>
-      </c>
-      <c r="C131" t="n">
         <v>8.72400134589502</v>
       </c>
     </row>
@@ -1803,9 +1407,6 @@
         <v>34639</v>
       </c>
       <c r="B132" t="n">
-        <v>0.633041666666667</v>
-      </c>
-      <c r="C132" t="n">
         <v>8.47162777777778</v>
       </c>
     </row>
@@ -1814,9 +1415,6 @@
         <v>34669</v>
       </c>
       <c r="B133" t="n">
-        <v>0.617758064516129</v>
-      </c>
-      <c r="C133" t="n">
         <v>8.24783870967742</v>
       </c>
     </row>
@@ -1825,9 +1423,6 @@
         <v>34700</v>
       </c>
       <c r="B134" t="n">
-        <v>0.424528225806452</v>
-      </c>
-      <c r="C134" t="n">
         <v>6.67302016129032</v>
       </c>
     </row>
@@ -1836,9 +1431,6 @@
         <v>34731</v>
       </c>
       <c r="B135" t="n">
-        <v>0.287575892857143</v>
-      </c>
-      <c r="C135" t="n">
         <v>5.60146875</v>
       </c>
     </row>
@@ -1847,9 +1439,6 @@
         <v>34759</v>
       </c>
       <c r="B136" t="n">
-        <v>0.302891129032258</v>
-      </c>
-      <c r="C136" t="n">
         <v>5.69281048387097</v>
       </c>
     </row>
@@ -1858,9 +1447,6 @@
         <v>34790</v>
       </c>
       <c r="B137" t="n">
-        <v>0.3011125</v>
-      </c>
-      <c r="C137" t="n">
         <v>5.71199166666667</v>
       </c>
     </row>
@@ -1869,9 +1455,6 @@
         <v>34820</v>
       </c>
       <c r="B138" t="n">
-        <v>0.316741935483871</v>
-      </c>
-      <c r="C138" t="n">
         <v>5.79937768817204</v>
       </c>
     </row>
@@ -1880,9 +1463,6 @@
         <v>34851</v>
       </c>
       <c r="B139" t="n">
-        <v>0.570941666666667</v>
-      </c>
-      <c r="C139" t="n">
         <v>7.72019166666667</v>
       </c>
     </row>
@@ -1891,9 +1471,6 @@
         <v>34881</v>
       </c>
       <c r="B140" t="n">
-        <v>0.669736559139785</v>
-      </c>
-      <c r="C140" t="n">
         <v>8.50138440860215</v>
       </c>
     </row>
@@ -1902,9 +1479,6 @@
         <v>34912</v>
       </c>
       <c r="B141" t="n">
-        <v>0.702668010752688</v>
-      </c>
-      <c r="C141" t="n">
         <v>8.83507930107527</v>
       </c>
     </row>
@@ -1913,9 +1487,6 @@
         <v>34943</v>
       </c>
       <c r="B142" t="n">
-        <v>0.731123611111111</v>
-      </c>
-      <c r="C142" t="n">
         <v>9.29739305555556</v>
       </c>
     </row>
@@ -1924,9 +1495,6 @@
         <v>34973</v>
       </c>
       <c r="B143" t="n">
-        <v>0.613535666218035</v>
-      </c>
-      <c r="C143" t="n">
         <v>8.31444279946164</v>
       </c>
     </row>
@@ -1935,9 +1503,6 @@
         <v>35004</v>
       </c>
       <c r="B144" t="n">
-        <v>0.606111111111111</v>
-      </c>
-      <c r="C144" t="n">
         <v>8.22850138888889</v>
       </c>
     </row>
@@ -1946,9 +1511,6 @@
         <v>35034</v>
       </c>
       <c r="B145" t="n">
-        <v>0.486540322580645</v>
-      </c>
-      <c r="C145" t="n">
         <v>7.20180913978495</v>
       </c>
     </row>
@@ -1957,9 +1519,6 @@
         <v>35065</v>
       </c>
       <c r="B146" t="n">
-        <v>0.428963709677419</v>
-      </c>
-      <c r="C146" t="n">
         <v>6.70235483870968</v>
       </c>
     </row>
@@ -1968,9 +1527,6 @@
         <v>35096</v>
       </c>
       <c r="B147" t="n">
-        <v>0.360066091954023</v>
-      </c>
-      <c r="C147" t="n">
         <v>6.12370402298851</v>
       </c>
     </row>
@@ -1979,9 +1535,6 @@
         <v>35125</v>
       </c>
       <c r="B148" t="n">
-        <v>0.205706989247312</v>
-      </c>
-      <c r="C148" t="n">
         <v>4.8179435483871</v>
       </c>
     </row>
@@ -1990,9 +1543,6 @@
         <v>35156</v>
       </c>
       <c r="B149" t="n">
-        <v>0.226408333333333</v>
-      </c>
-      <c r="C149" t="n">
         <v>4.96491944444444</v>
       </c>
     </row>
@@ -2001,9 +1551,6 @@
         <v>35186</v>
       </c>
       <c r="B150" t="n">
-        <v>0.350385752688172</v>
-      </c>
-      <c r="C150" t="n">
         <v>6.01501612903226</v>
       </c>
     </row>
@@ -2012,9 +1559,6 @@
         <v>35217</v>
       </c>
       <c r="B151" t="n">
-        <v>0.598806944444444</v>
-      </c>
-      <c r="C151" t="n">
         <v>7.94389027777778</v>
       </c>
     </row>
@@ -2023,9 +1567,6 @@
         <v>35247</v>
       </c>
       <c r="B152" t="n">
-        <v>0.663111559139785</v>
-      </c>
-      <c r="C152" t="n">
         <v>8.48127016129032</v>
       </c>
     </row>
@@ -2034,9 +1575,6 @@
         <v>35278</v>
       </c>
       <c r="B153" t="n">
-        <v>0.69023252688172</v>
-      </c>
-      <c r="C153" t="n">
         <v>8.72599462365591</v>
       </c>
     </row>
@@ -2045,9 +1583,6 @@
         <v>35309</v>
       </c>
       <c r="B154" t="n">
-        <v>0.714243055555556</v>
-      </c>
-      <c r="C154" t="n">
         <v>9.1014</v>
       </c>
     </row>
@@ -2056,9 +1591,6 @@
         <v>35339</v>
       </c>
       <c r="B155" t="n">
-        <v>0.688864064602961</v>
-      </c>
-      <c r="C155" t="n">
         <v>8.89306594885599</v>
       </c>
     </row>
@@ -2067,9 +1599,6 @@
         <v>35370</v>
       </c>
       <c r="B156" t="n">
-        <v>0.585906944444444</v>
-      </c>
-      <c r="C156" t="n">
         <v>7.99751666666667</v>
       </c>
     </row>
@@ -2078,9 +1607,6 @@
         <v>35400</v>
       </c>
       <c r="B157" t="n">
-        <v>0.591715053763441</v>
-      </c>
-      <c r="C157" t="n">
         <v>8.01828897849462</v>
       </c>
     </row>
@@ -2089,9 +1615,6 @@
         <v>35431</v>
       </c>
       <c r="B158" t="n">
-        <v>0.453754032258065</v>
-      </c>
-      <c r="C158" t="n">
         <v>6.89062768817204</v>
       </c>
     </row>
@@ -2100,9 +1623,6 @@
         <v>35462</v>
       </c>
       <c r="B159" t="n">
-        <v>0.525979166666667</v>
-      </c>
-      <c r="C159" t="n">
         <v>7.42290773809524</v>
       </c>
     </row>
@@ -2111,9 +1631,6 @@
         <v>35490</v>
       </c>
       <c r="B160" t="n">
-        <v>0.409489247311828</v>
-      </c>
-      <c r="C160" t="n">
         <v>6.56735349462366</v>
       </c>
     </row>
@@ -2122,9 +1639,6 @@
         <v>35521</v>
       </c>
       <c r="B161" t="n">
-        <v>0.340454166666667</v>
-      </c>
-      <c r="C161" t="n">
         <v>5.9843625</v>
       </c>
     </row>
@@ -2133,9 +1647,6 @@
         <v>35551</v>
       </c>
       <c r="B162" t="n">
-        <v>0.518873655913978</v>
-      </c>
-      <c r="C162" t="n">
         <v>7.36745564516129</v>
       </c>
     </row>
@@ -2144,9 +1655,6 @@
         <v>35582</v>
       </c>
       <c r="B163" t="n">
-        <v>0.539443055555556</v>
-      </c>
-      <c r="C163" t="n">
         <v>7.50909166666667</v>
       </c>
     </row>
@@ -2155,9 +1663,6 @@
         <v>35612</v>
       </c>
       <c r="B164" t="n">
-        <v>0.659698924731183</v>
-      </c>
-      <c r="C164" t="n">
         <v>8.42966129032258</v>
       </c>
     </row>
@@ -2166,9 +1671,6 @@
         <v>35643</v>
       </c>
       <c r="B165" t="n">
-        <v>0.701516129032258</v>
-      </c>
-      <c r="C165" t="n">
         <v>8.89892607526882</v>
       </c>
     </row>
@@ -2177,9 +1679,6 @@
         <v>35674</v>
       </c>
       <c r="B166" t="n">
-        <v>0.542755555555556</v>
-      </c>
-      <c r="C166" t="n">
         <v>7.65127083333333</v>
       </c>
     </row>
@@ -2188,9 +1687,6 @@
         <v>35704</v>
       </c>
       <c r="B167" t="n">
-        <v>0.565624495289367</v>
-      </c>
-      <c r="C167" t="n">
         <v>7.8782597577389</v>
       </c>
     </row>
@@ -2199,9 +1695,6 @@
         <v>35735</v>
       </c>
       <c r="B168" t="n">
-        <v>0.554766666666667</v>
-      </c>
-      <c r="C168" t="n">
         <v>7.788825</v>
       </c>
     </row>
@@ -2210,9 +1703,6 @@
         <v>35765</v>
       </c>
       <c r="B169" t="n">
-        <v>0.471047043010753</v>
-      </c>
-      <c r="C169" t="n">
         <v>7.06369623655914</v>
       </c>
     </row>
@@ -2221,9 +1711,6 @@
         <v>35796</v>
       </c>
       <c r="B170" t="n">
-        <v>0.358629032258065</v>
-      </c>
-      <c r="C170" t="n">
         <v>6.15061155913978</v>
       </c>
     </row>
@@ -2232,9 +1719,6 @@
         <v>35827</v>
       </c>
       <c r="B171" t="n">
-        <v>0.493633928571429</v>
-      </c>
-      <c r="C171" t="n">
         <v>7.19459226190476</v>
       </c>
     </row>
@@ -2243,9 +1727,6 @@
         <v>35855</v>
       </c>
       <c r="B172" t="n">
-        <v>0.418625</v>
-      </c>
-      <c r="C172" t="n">
         <v>6.62032795698925</v>
       </c>
     </row>
@@ -2254,9 +1735,6 @@
         <v>35886</v>
       </c>
       <c r="B173" t="n">
-        <v>0.499731944444444</v>
-      </c>
-      <c r="C173" t="n">
         <v>7.21094861111111</v>
       </c>
     </row>
@@ -2265,9 +1743,6 @@
         <v>35916</v>
       </c>
       <c r="B174" t="n">
-        <v>0.575297043010753</v>
-      </c>
-      <c r="C174" t="n">
         <v>7.80138306451613</v>
       </c>
     </row>
@@ -2276,9 +1751,6 @@
         <v>35947</v>
       </c>
       <c r="B175" t="n">
-        <v>0.644334722222222</v>
-      </c>
-      <c r="C175" t="n">
         <v>8.31645555555555</v>
       </c>
     </row>
@@ -2287,9 +1759,6 @@
         <v>35977</v>
       </c>
       <c r="B176" t="n">
-        <v>0.660563172043011</v>
-      </c>
-      <c r="C176" t="n">
         <v>8.45844086021505</v>
       </c>
     </row>
@@ -2298,9 +1767,6 @@
         <v>36008</v>
       </c>
       <c r="B177" t="n">
-        <v>0.691298387096774</v>
-      </c>
-      <c r="C177" t="n">
         <v>8.77597446236559</v>
       </c>
     </row>
@@ -2309,9 +1775,6 @@
         <v>36039</v>
       </c>
       <c r="B178" t="n">
-        <v>0.693036111111111</v>
-      </c>
-      <c r="C178" t="n">
         <v>8.969975</v>
       </c>
     </row>
@@ -2320,9 +1783,6 @@
         <v>36069</v>
       </c>
       <c r="B179" t="n">
-        <v>0.690189771197847</v>
-      </c>
-      <c r="C179" t="n">
         <v>8.99546298788695</v>
       </c>
     </row>
@@ -2331,9 +1791,6 @@
         <v>36100</v>
       </c>
       <c r="B180" t="n">
-        <v>0.549158333333333</v>
-      </c>
-      <c r="C180" t="n">
         <v>7.773075</v>
       </c>
     </row>
@@ -2342,9 +1799,6 @@
         <v>36130</v>
       </c>
       <c r="B181" t="n">
-        <v>0.589141129032258</v>
-      </c>
-      <c r="C181" t="n">
         <v>8.10423790322581</v>
       </c>
     </row>
@@ -2353,9 +1807,6 @@
         <v>36161</v>
       </c>
       <c r="B182" t="n">
-        <v>0.446614247311828</v>
-      </c>
-      <c r="C182" t="n">
         <v>6.8489502688172</v>
       </c>
     </row>
@@ -2364,9 +1815,6 @@
         <v>36192</v>
       </c>
       <c r="B183" t="n">
-        <v>0.489683035714286</v>
-      </c>
-      <c r="C183" t="n">
         <v>7.14107142857143</v>
       </c>
     </row>
@@ -2375,9 +1823,6 @@
         <v>36220</v>
       </c>
       <c r="B184" t="n">
-        <v>0.353430107526882</v>
-      </c>
-      <c r="C184" t="n">
         <v>6.09107795698925</v>
       </c>
     </row>
@@ -2386,9 +1831,6 @@
         <v>36251</v>
       </c>
       <c r="B185" t="n">
-        <v>0.433072222222222</v>
-      </c>
-      <c r="C185" t="n">
         <v>6.71430555555556</v>
       </c>
     </row>
@@ -2397,9 +1839,6 @@
         <v>36281</v>
       </c>
       <c r="B186" t="n">
-        <v>0.399103494623656</v>
-      </c>
-      <c r="C186" t="n">
         <v>6.38736290322581</v>
       </c>
     </row>
@@ -2408,9 +1847,6 @@
         <v>36312</v>
       </c>
       <c r="B187" t="n">
-        <v>0.577970833333333</v>
-      </c>
-      <c r="C187" t="n">
         <v>7.80222222222222</v>
       </c>
     </row>
@@ -2419,9 +1855,6 @@
         <v>36342</v>
       </c>
       <c r="B188" t="n">
-        <v>0.68909811827957</v>
-      </c>
-      <c r="C188" t="n">
         <v>8.71875268817204</v>
       </c>
     </row>
@@ -2430,9 +1863,6 @@
         <v>36373</v>
       </c>
       <c r="B189" t="n">
-        <v>0.733685483870968</v>
-      </c>
-      <c r="C189" t="n">
         <v>9.19049193548387</v>
       </c>
     </row>
@@ -2441,9 +1871,6 @@
         <v>36404</v>
       </c>
       <c r="B190" t="n">
-        <v>0.706215277777778</v>
-      </c>
-      <c r="C190" t="n">
         <v>9.09954305555556</v>
       </c>
     </row>
@@ -2452,9 +1879,6 @@
         <v>36434</v>
       </c>
       <c r="B191" t="n">
-        <v>0.606907133243607</v>
-      </c>
-      <c r="C191" t="n">
         <v>8.25191117092867</v>
       </c>
     </row>
@@ -2463,9 +1887,6 @@
         <v>36465</v>
       </c>
       <c r="B192" t="n">
-        <v>0.538234722222222</v>
-      </c>
-      <c r="C192" t="n">
         <v>7.59164861111111</v>
       </c>
     </row>
@@ -2474,9 +1895,6 @@
         <v>36495</v>
       </c>
       <c r="B193" t="n">
-        <v>0.565240591397849</v>
-      </c>
-      <c r="C193" t="n">
         <v>7.79217204301075</v>
       </c>
     </row>
@@ -2485,9 +1903,6 @@
         <v>36526</v>
       </c>
       <c r="B194" t="n">
-        <v>0.373715053763441</v>
-      </c>
-      <c r="C194" t="n">
         <v>6.26296370967742</v>
       </c>
     </row>
@@ -2496,9 +1911,6 @@
         <v>36557</v>
       </c>
       <c r="B195" t="n">
-        <v>0.282652298850575</v>
-      </c>
-      <c r="C195" t="n">
         <v>5.45714511494253</v>
       </c>
     </row>
@@ -2507,9 +1919,6 @@
         <v>36586</v>
       </c>
       <c r="B196" t="n">
-        <v>0.363814516129032</v>
-      </c>
-      <c r="C196" t="n">
         <v>6.18245295698925</v>
       </c>
     </row>
@@ -2518,9 +1927,6 @@
         <v>36617</v>
       </c>
       <c r="B197" t="n">
-        <v>0.375066666666667</v>
-      </c>
-      <c r="C197" t="n">
         <v>6.24925694444444</v>
       </c>
     </row>
@@ -2529,9 +1935,6 @@
         <v>36647</v>
       </c>
       <c r="B198" t="n">
-        <v>0.498252688172043</v>
-      </c>
-      <c r="C198" t="n">
         <v>7.19321370967742</v>
       </c>
     </row>
@@ -2540,9 +1943,6 @@
         <v>36678</v>
       </c>
       <c r="B199" t="n">
-        <v>0.566784722222222</v>
-      </c>
-      <c r="C199" t="n">
         <v>7.74060416666667</v>
       </c>
     </row>
@@ -2551,9 +1951,6 @@
         <v>36708</v>
       </c>
       <c r="B200" t="n">
-        <v>0.615266129032258</v>
-      </c>
-      <c r="C200" t="n">
         <v>8.06404704301075</v>
       </c>
     </row>
@@ -2562,9 +1959,6 @@
         <v>36739</v>
       </c>
       <c r="B201" t="n">
-        <v>0.648825268817204</v>
-      </c>
-      <c r="C201" t="n">
         <v>8.36547580645161</v>
       </c>
     </row>
@@ -2573,9 +1967,6 @@
         <v>36770</v>
       </c>
       <c r="B202" t="n">
-        <v>0.692877777777778</v>
-      </c>
-      <c r="C202" t="n">
         <v>8.81101111111111</v>
       </c>
     </row>
@@ -2584,9 +1975,6 @@
         <v>36800</v>
       </c>
       <c r="B203" t="n">
-        <v>0.690522207267833</v>
-      </c>
-      <c r="C203" t="n">
         <v>8.88338358008075</v>
       </c>
     </row>
@@ -2595,9 +1983,6 @@
         <v>36831</v>
       </c>
       <c r="B204" t="n">
-        <v>0.606404166666667</v>
-      </c>
-      <c r="C204" t="n">
         <v>8.17578333333333</v>
       </c>
     </row>
@@ -2606,9 +1991,6 @@
         <v>36861</v>
       </c>
       <c r="B205" t="n">
-        <v>0.453342741935484</v>
-      </c>
-      <c r="C205" t="n">
         <v>6.89501209677419</v>
       </c>
     </row>
@@ -2617,9 +1999,6 @@
         <v>36892</v>
       </c>
       <c r="B206" t="n">
-        <v>0.546262096774194</v>
-      </c>
-      <c r="C206" t="n">
         <v>7.62470430107527</v>
       </c>
     </row>
@@ -2628,9 +2007,6 @@
         <v>36923</v>
       </c>
       <c r="B207" t="n">
-        <v>0.349927083333333</v>
-      </c>
-      <c r="C207" t="n">
         <v>6.08555803571429</v>
       </c>
     </row>
@@ -2639,9 +2015,6 @@
         <v>36951</v>
       </c>
       <c r="B208" t="n">
-        <v>0.297520161290323</v>
-      </c>
-      <c r="C208" t="n">
         <v>5.63473521505376</v>
       </c>
     </row>
@@ -2650,9 +2023,6 @@
         <v>36982</v>
       </c>
       <c r="B209" t="n">
-        <v>0.395588888888889</v>
-      </c>
-      <c r="C209" t="n">
         <v>6.36397638888889</v>
       </c>
     </row>
@@ -2661,9 +2031,6 @@
         <v>37012</v>
       </c>
       <c r="B210" t="n">
-        <v>0.407465053763441</v>
-      </c>
-      <c r="C210" t="n">
         <v>6.49006182795699</v>
       </c>
     </row>
@@ -2672,9 +2039,6 @@
         <v>37043</v>
       </c>
       <c r="B211" t="n">
-        <v>0.556618055555556</v>
-      </c>
-      <c r="C211" t="n">
         <v>7.6284125</v>
       </c>
     </row>
@@ -2683,9 +2047,6 @@
         <v>37073</v>
       </c>
       <c r="B212" t="n">
-        <v>0.623072580645161</v>
-      </c>
-      <c r="C212" t="n">
         <v>8.14901344086021</v>
       </c>
     </row>
@@ -2694,9 +2055,6 @@
         <v>37104</v>
       </c>
       <c r="B213" t="n">
-        <v>0.743439516129032</v>
-      </c>
-      <c r="C213" t="n">
         <v>9.16383064516129</v>
       </c>
     </row>
@@ -2705,9 +2063,6 @@
         <v>37135</v>
       </c>
       <c r="B214" t="n">
-        <v>0.647168055555556</v>
-      </c>
-      <c r="C214" t="n">
         <v>8.46336805555556</v>
       </c>
     </row>
@@ -2716,9 +2071,6 @@
         <v>37165</v>
       </c>
       <c r="B215" t="n">
-        <v>0.572410497981158</v>
-      </c>
-      <c r="C215" t="n">
         <v>7.84861776581427</v>
       </c>
     </row>
@@ -2727,9 +2079,6 @@
         <v>37196</v>
       </c>
       <c r="B216" t="n">
-        <v>0.563744444444444</v>
-      </c>
-      <c r="C216" t="n">
         <v>7.84474027777778</v>
       </c>
     </row>
@@ -2738,9 +2087,6 @@
         <v>37226</v>
       </c>
       <c r="B217" t="n">
-        <v>0.679573924731183</v>
-      </c>
-      <c r="C217" t="n">
         <v>8.68167607526882</v>
       </c>
     </row>
@@ -2749,9 +2095,6 @@
         <v>37257</v>
       </c>
       <c r="B218" t="n">
-        <v>0.326662634408602</v>
-      </c>
-      <c r="C218" t="n">
         <v>5.8970376344086</v>
       </c>
     </row>
@@ -2760,9 +2103,6 @@
         <v>37288</v>
       </c>
       <c r="B219" t="n">
-        <v>0.393739583333333</v>
-      </c>
-      <c r="C219" t="n">
         <v>6.4220119047619</v>
       </c>
     </row>
@@ -2771,9 +2111,6 @@
         <v>37316</v>
       </c>
       <c r="B220" t="n">
-        <v>0.373510752688172</v>
-      </c>
-      <c r="C220" t="n">
         <v>6.22110080645161</v>
       </c>
     </row>
@@ -2782,9 +2119,6 @@
         <v>37347</v>
       </c>
       <c r="B221" t="n">
-        <v>0.353947222222222</v>
-      </c>
-      <c r="C221" t="n">
         <v>5.94695694444444</v>
       </c>
     </row>
@@ -2793,9 +2127,6 @@
         <v>37377</v>
       </c>
       <c r="B222" t="n">
-        <v>0.441043010752688</v>
-      </c>
-      <c r="C222" t="n">
         <v>6.73917204301075</v>
       </c>
     </row>
@@ -2804,9 +2135,6 @@
         <v>37408</v>
       </c>
       <c r="B223" t="n">
-        <v>0.564020833333333</v>
-      </c>
-      <c r="C223" t="n">
         <v>7.68944027777778</v>
       </c>
     </row>
@@ -2815,9 +2143,6 @@
         <v>37438</v>
       </c>
       <c r="B224" t="n">
-        <v>0.587290322580645</v>
-      </c>
-      <c r="C224" t="n">
         <v>7.8704247311828</v>
       </c>
     </row>
@@ -2826,9 +2151,6 @@
         <v>37469</v>
       </c>
       <c r="B225" t="n">
-        <v>0.722185483870968</v>
-      </c>
-      <c r="C225" t="n">
         <v>9.06566129032258</v>
       </c>
     </row>
@@ -2837,9 +2159,6 @@
         <v>37500</v>
       </c>
       <c r="B226" t="n">
-        <v>0.616288888888889</v>
-      </c>
-      <c r="C226" t="n">
         <v>8.26876527777778</v>
       </c>
     </row>
@@ -2848,9 +2167,6 @@
         <v>37530</v>
       </c>
       <c r="B227" t="n">
-        <v>0.71085752688172</v>
-      </c>
-      <c r="C227" t="n">
         <v>9.16898655913979</v>
       </c>
     </row>
@@ -2859,9 +2175,6 @@
         <v>37561</v>
       </c>
       <c r="B228" t="n">
-        <v>0.633037552155772</v>
-      </c>
-      <c r="C228" t="n">
         <v>8.41942559109875</v>
       </c>
     </row>
@@ -2870,9 +2183,6 @@
         <v>37591</v>
       </c>
       <c r="B229" t="n">
-        <v>0.547139784946237</v>
-      </c>
-      <c r="C229" t="n">
         <v>7.65183064516129</v>
       </c>
     </row>
@@ -2881,9 +2191,6 @@
         <v>37622</v>
       </c>
       <c r="B230" t="n">
-        <v>0.363602150537634</v>
-      </c>
-      <c r="C230" t="n">
         <v>6.17835349462366</v>
       </c>
     </row>
@@ -2892,9 +2199,6 @@
         <v>37653</v>
       </c>
       <c r="B231" t="n">
-        <v>0.388321428571429</v>
-      </c>
-      <c r="C231" t="n">
         <v>6.35134523809524</v>
       </c>
     </row>
@@ -2903,9 +2207,6 @@
         <v>37681</v>
       </c>
       <c r="B232" t="n">
-        <v>0.319764784946237</v>
-      </c>
-      <c r="C232" t="n">
         <v>5.85786155913978</v>
       </c>
     </row>
@@ -2914,9 +2215,6 @@
         <v>37712</v>
       </c>
       <c r="B233" t="n">
-        <v>0.353944444444444</v>
-      </c>
-      <c r="C233" t="n">
         <v>6.05286111111111</v>
       </c>
     </row>
@@ -2925,9 +2223,6 @@
         <v>37742</v>
       </c>
       <c r="B234" t="n">
-        <v>0.412689516129032</v>
-      </c>
-      <c r="C234" t="n">
         <v>6.52791129032258</v>
       </c>
     </row>
@@ -2936,9 +2231,6 @@
         <v>37773</v>
       </c>
       <c r="B235" t="n">
-        <v>0.56535</v>
-      </c>
-      <c r="C235" t="n">
         <v>7.68345</v>
       </c>
     </row>
@@ -2947,9 +2239,6 @@
         <v>37803</v>
       </c>
       <c r="B236" t="n">
-        <v>0.679486559139785</v>
-      </c>
-      <c r="C236" t="n">
         <v>8.65287096774193</v>
       </c>
     </row>
@@ -2958,9 +2247,6 @@
         <v>37834</v>
       </c>
       <c r="B237" t="n">
-        <v>0.640572580645161</v>
-      </c>
-      <c r="C237" t="n">
         <v>8.33254838709677</v>
       </c>
     </row>
@@ -2969,9 +2255,6 @@
         <v>37865</v>
       </c>
       <c r="B238" t="n">
-        <v>0.707613888888889</v>
-      </c>
-      <c r="C238" t="n">
         <v>9.00929444444444</v>
       </c>
     </row>
@@ -2980,9 +2263,6 @@
         <v>37895</v>
       </c>
       <c r="B239" t="n">
-        <v>0.683298788694482</v>
-      </c>
-      <c r="C239" t="n">
         <v>8.8819730820996</v>
       </c>
     </row>
@@ -2991,9 +2271,6 @@
         <v>37926</v>
       </c>
       <c r="B240" t="n">
-        <v>0.5986</v>
-      </c>
-      <c r="C240" t="n">
         <v>8.14521944444444</v>
       </c>
     </row>
@@ -3002,9 +2279,6 @@
         <v>37956</v>
       </c>
       <c r="B241" t="n">
-        <v>0.583913978494624</v>
-      </c>
-      <c r="C241" t="n">
         <v>7.95180376344086</v>
       </c>
     </row>
@@ -3013,9 +2287,6 @@
         <v>37987</v>
       </c>
       <c r="B242" t="n">
-        <v>0.312403225806452</v>
-      </c>
-      <c r="C242" t="n">
         <v>5.730875</v>
       </c>
     </row>
@@ -3024,9 +2295,6 @@
         <v>38018</v>
       </c>
       <c r="B243" t="n">
-        <v>0.359318965517241</v>
-      </c>
-      <c r="C243" t="n">
         <v>6.16054885057471</v>
       </c>
     </row>
@@ -3035,9 +2303,6 @@
         <v>38047</v>
       </c>
       <c r="B244" t="n">
-        <v>0.447240591397849</v>
-      </c>
-      <c r="C244" t="n">
         <v>6.82413440860215</v>
       </c>
     </row>
@@ -3046,9 +2311,6 @@
         <v>38078</v>
       </c>
       <c r="B245" t="n">
-        <v>0.446309722222222</v>
-      </c>
-      <c r="C245" t="n">
         <v>6.81194166666667</v>
       </c>
     </row>
@@ -3057,9 +2319,6 @@
         <v>38108</v>
       </c>
       <c r="B246" t="n">
-        <v>0.452344086021505</v>
-      </c>
-      <c r="C246" t="n">
         <v>6.84951612903226</v>
       </c>
     </row>
@@ -3068,9 +2327,6 @@
         <v>38139</v>
       </c>
       <c r="B247" t="n">
-        <v>0.557045833333333</v>
-      </c>
-      <c r="C247" t="n">
         <v>7.66544166666667</v>
       </c>
     </row>
@@ -3079,9 +2335,6 @@
         <v>38169</v>
       </c>
       <c r="B248" t="n">
-        <v>0.580177419354839</v>
-      </c>
-      <c r="C248" t="n">
         <v>7.8971438172043</v>
       </c>
     </row>
@@ -3090,9 +2343,6 @@
         <v>38200</v>
       </c>
       <c r="B249" t="n">
-        <v>0.665326612903226</v>
-      </c>
-      <c r="C249" t="n">
         <v>8.51998655913978</v>
       </c>
     </row>
@@ -3101,9 +2351,6 @@
         <v>38231</v>
       </c>
       <c r="B250" t="n">
-        <v>0.750841666666667</v>
-      </c>
-      <c r="C250" t="n">
         <v>9.39755138888889</v>
       </c>
     </row>
@@ -3112,9 +2359,6 @@
         <v>38261</v>
       </c>
       <c r="B251" t="n">
-        <v>0.648967741935484</v>
-      </c>
-      <c r="C251" t="n">
         <v>8.59660752688172</v>
       </c>
     </row>
@@ -3123,9 +2367,6 @@
         <v>38292</v>
       </c>
       <c r="B252" t="n">
-        <v>0.644225312934631</v>
-      </c>
-      <c r="C252" t="n">
         <v>8.51758692628651</v>
       </c>
     </row>
@@ -3134,9 +2375,6 @@
         <v>38322</v>
       </c>
       <c r="B253" t="n">
-        <v>0.543684139784946</v>
-      </c>
-      <c r="C253" t="n">
         <v>7.62755913978495</v>
       </c>
     </row>
@@ -3145,9 +2383,6 @@
         <v>38353</v>
       </c>
       <c r="B254" t="n">
-        <v>0.414217741935484</v>
-      </c>
-      <c r="C254" t="n">
         <v>6.59950268817204</v>
       </c>
     </row>
@@ -3156,9 +2391,6 @@
         <v>38384</v>
       </c>
       <c r="B255" t="n">
-        <v>0.425404761904762</v>
-      </c>
-      <c r="C255" t="n">
         <v>6.67121577380952</v>
       </c>
     </row>
@@ -3167,9 +2399,6 @@
         <v>38412</v>
       </c>
       <c r="B256" t="n">
-        <v>0.311670698924731</v>
-      </c>
-      <c r="C256" t="n">
         <v>5.71860887096774</v>
       </c>
     </row>
@@ -3178,9 +2407,6 @@
         <v>38443</v>
       </c>
       <c r="B257" t="n">
-        <v>0.409329166666667</v>
-      </c>
-      <c r="C257" t="n">
         <v>6.48609861111111</v>
       </c>
     </row>
@@ -3189,9 +2415,6 @@
         <v>38473</v>
       </c>
       <c r="B258" t="n">
-        <v>0.458461021505376</v>
-      </c>
-      <c r="C258" t="n">
         <v>6.84671102150538</v>
       </c>
     </row>
@@ -3200,9 +2423,6 @@
         <v>38504</v>
       </c>
       <c r="B259" t="n">
-        <v>0.549618055555556</v>
-      </c>
-      <c r="C259" t="n">
         <v>7.63291666666667</v>
       </c>
     </row>
@@ -3211,9 +2431,6 @@
         <v>38534</v>
       </c>
       <c r="B260" t="n">
-        <v>0.620215053763441</v>
-      </c>
-      <c r="C260" t="n">
         <v>8.15311155913978</v>
       </c>
     </row>
@@ -3222,9 +2439,6 @@
         <v>38565</v>
       </c>
       <c r="B261" t="n">
-        <v>0.705736559139785</v>
-      </c>
-      <c r="C261" t="n">
         <v>8.84542338709677</v>
       </c>
     </row>
@@ -3233,9 +2447,6 @@
         <v>38596</v>
       </c>
       <c r="B262" t="n">
-        <v>0.669483333333333</v>
-      </c>
-      <c r="C262" t="n">
         <v>8.59978055555556</v>
       </c>
     </row>
@@ -3244,9 +2455,6 @@
         <v>38626</v>
       </c>
       <c r="B263" t="n">
-        <v>0.700794078061911</v>
-      </c>
-      <c r="C263" t="n">
         <v>9.05509555854643</v>
       </c>
     </row>
@@ -3255,9 +2463,6 @@
         <v>38657</v>
       </c>
       <c r="B264" t="n">
-        <v>0.659422222222222</v>
-      </c>
-      <c r="C264" t="n">
         <v>8.61629444444444</v>
       </c>
     </row>
@@ -3266,9 +2471,6 @@
         <v>38687</v>
       </c>
       <c r="B265" t="n">
-        <v>0.542556451612903</v>
-      </c>
-      <c r="C265" t="n">
         <v>7.53570161290323</v>
       </c>
     </row>
@@ -3277,9 +2479,6 @@
         <v>38718</v>
       </c>
       <c r="B266" t="n">
-        <v>0.615520161290323</v>
-      </c>
-      <c r="C266" t="n">
         <v>8.15043279569892</v>
       </c>
     </row>
@@ -3288,9 +2487,6 @@
         <v>38749</v>
       </c>
       <c r="B267" t="n">
-        <v>0.280160714285714</v>
-      </c>
-      <c r="C267" t="n">
         <v>5.47374851190476</v>
       </c>
     </row>
@@ -3299,9 +2495,6 @@
         <v>38777</v>
       </c>
       <c r="B268" t="n">
-        <v>0.270904569892473</v>
-      </c>
-      <c r="C268" t="n">
         <v>5.46193010752688</v>
       </c>
     </row>
@@ -3310,9 +2503,6 @@
         <v>38808</v>
       </c>
       <c r="B269" t="n">
-        <v>0.222126388888889</v>
-      </c>
-      <c r="C269" t="n">
         <v>4.92881527777778</v>
       </c>
     </row>
@@ -3321,9 +2511,6 @@
         <v>38838</v>
       </c>
       <c r="B270" t="n">
-        <v>0.397185483870968</v>
-      </c>
-      <c r="C270" t="n">
         <v>6.44395833333333</v>
       </c>
     </row>
@@ -3332,9 +2519,6 @@
         <v>38869</v>
       </c>
       <c r="B271" t="n">
-        <v>0.605297222222222</v>
-      </c>
-      <c r="C271" t="n">
         <v>8.00618333333333</v>
       </c>
     </row>
@@ -3343,9 +2527,6 @@
         <v>38899</v>
       </c>
       <c r="B272" t="n">
-        <v>0.623387096774194</v>
-      </c>
-      <c r="C272" t="n">
         <v>8.17702688172043</v>
       </c>
     </row>
@@ -3354,9 +2535,6 @@
         <v>38930</v>
       </c>
       <c r="B273" t="n">
-        <v>0.667252688172043</v>
-      </c>
-      <c r="C273" t="n">
         <v>8.53825806451613</v>
       </c>
     </row>
@@ -3365,9 +2543,6 @@
         <v>38961</v>
       </c>
       <c r="B274" t="n">
-        <v>0.652255555555556</v>
-      </c>
-      <c r="C274" t="n">
         <v>8.43165972222222</v>
       </c>
     </row>
@@ -3376,9 +2551,6 @@
         <v>38991</v>
       </c>
       <c r="B275" t="n">
-        <v>0.623986559139785</v>
-      </c>
-      <c r="C275" t="n">
         <v>8.21365456989247</v>
       </c>
     </row>
@@ -3387,9 +2559,6 @@
         <v>39022</v>
       </c>
       <c r="B276" t="n">
-        <v>0.603738525730181</v>
-      </c>
-      <c r="C276" t="n">
         <v>8.12346870653686</v>
       </c>
     </row>
@@ -3398,9 +2567,6 @@
         <v>39052</v>
       </c>
       <c r="B277" t="n">
-        <v>0.549432795698925</v>
-      </c>
-      <c r="C277" t="n">
         <v>7.63502956989247</v>
       </c>
     </row>
@@ -3409,9 +2575,6 @@
         <v>39083</v>
       </c>
       <c r="B278" t="n">
-        <v>0.52533064516129</v>
-      </c>
-      <c r="C278" t="n">
         <v>7.44801612903226</v>
       </c>
     </row>
@@ -3420,9 +2583,6 @@
         <v>39114</v>
       </c>
       <c r="B279" t="n">
-        <v>0.321247023809524</v>
-      </c>
-      <c r="C279" t="n">
         <v>5.79867708333333</v>
       </c>
     </row>
@@ -3431,9 +2591,6 @@
         <v>39142</v>
       </c>
       <c r="B280" t="n">
-        <v>0.440752688172043</v>
-      </c>
-      <c r="C280" t="n">
         <v>6.77365322580645</v>
       </c>
     </row>
@@ -3442,9 +2599,6 @@
         <v>39173</v>
       </c>
       <c r="B281" t="n">
-        <v>0.348191666666667</v>
-      </c>
-      <c r="C281" t="n">
         <v>6.05093472222222</v>
       </c>
     </row>
@@ -3453,9 +2607,6 @@
         <v>39203</v>
       </c>
       <c r="B282" t="n">
-        <v>0.482474462365591</v>
-      </c>
-      <c r="C282" t="n">
         <v>7.09643413978495</v>
       </c>
     </row>
@@ -3464,9 +2615,6 @@
         <v>39234</v>
       </c>
       <c r="B283" t="n">
-        <v>0.6334</v>
-      </c>
-      <c r="C283" t="n">
         <v>8.2526375</v>
       </c>
     </row>
@@ -3475,9 +2623,6 @@
         <v>39264</v>
       </c>
       <c r="B284" t="n">
-        <v>0.627612903225806</v>
-      </c>
-      <c r="C284" t="n">
         <v>8.20367338709677</v>
       </c>
     </row>
@@ -3486,9 +2631,6 @@
         <v>39295</v>
       </c>
       <c r="B285" t="n">
-        <v>0.762040322580645</v>
-      </c>
-      <c r="C285" t="n">
         <v>9.44137903225806</v>
       </c>
     </row>
@@ -3497,9 +2639,6 @@
         <v>39326</v>
       </c>
       <c r="B286" t="n">
-        <v>0.794622222222222</v>
-      </c>
-      <c r="C286" t="n">
         <v>9.81979444444444</v>
       </c>
     </row>
@@ -3508,9 +2647,6 @@
         <v>39356</v>
       </c>
       <c r="B287" t="n">
-        <v>0.733193808882907</v>
-      </c>
-      <c r="C287" t="n">
         <v>9.33498250336474</v>
       </c>
     </row>
@@ -3519,9 +2655,6 @@
         <v>39387</v>
       </c>
       <c r="B288" t="n">
-        <v>0.643404166666667</v>
-      </c>
-      <c r="C288" t="n">
         <v>8.53497083333333</v>
       </c>
     </row>
@@ -3530,9 +2663,6 @@
         <v>39417</v>
       </c>
       <c r="B289" t="n">
-        <v>0.560655913978495</v>
-      </c>
-      <c r="C289" t="n">
         <v>7.76985080645161</v>
       </c>
     </row>
@@ -3541,9 +2671,6 @@
         <v>39448</v>
       </c>
       <c r="B290" t="n">
-        <v>0.432861559139785</v>
-      </c>
-      <c r="C290" t="n">
         <v>6.68386290322581</v>
       </c>
     </row>
@@ -3552,9 +2679,6 @@
         <v>39479</v>
       </c>
       <c r="B291" t="n">
-        <v>0.345948275862069</v>
-      </c>
-      <c r="C291" t="n">
         <v>6.00710632183908</v>
       </c>
     </row>
@@ -3563,9 +2687,6 @@
         <v>39508</v>
       </c>
       <c r="B292" t="n">
-        <v>0.175497311827957</v>
-      </c>
-      <c r="C292" t="n">
         <v>4.45343548387097</v>
       </c>
     </row>
@@ -3574,9 +2695,6 @@
         <v>39539</v>
       </c>
       <c r="B293" t="n">
-        <v>0.269091666666667</v>
-      </c>
-      <c r="C293" t="n">
         <v>5.40912222222222</v>
       </c>
     </row>
@@ -3585,9 +2703,6 @@
         <v>39569</v>
       </c>
       <c r="B294" t="n">
-        <v>0.375927419354839</v>
-      </c>
-      <c r="C294" t="n">
         <v>6.18694489247312</v>
       </c>
     </row>
@@ -3596,9 +2711,6 @@
         <v>39600</v>
       </c>
       <c r="B295" t="n">
-        <v>0.579572222222222</v>
-      </c>
-      <c r="C295" t="n">
         <v>7.81157361111111</v>
       </c>
     </row>
@@ -3607,9 +2719,6 @@
         <v>39630</v>
       </c>
       <c r="B296" t="n">
-        <v>0.695983870967742</v>
-      </c>
-      <c r="C296" t="n">
         <v>8.73142741935484</v>
       </c>
     </row>
@@ -3618,9 +2727,6 @@
         <v>39661</v>
       </c>
       <c r="B297" t="n">
-        <v>0.660137096774194</v>
-      </c>
-      <c r="C297" t="n">
         <v>8.4291626344086</v>
       </c>
     </row>
@@ -3629,9 +2735,6 @@
         <v>39692</v>
       </c>
       <c r="B298" t="n">
-        <v>0.731884722222222</v>
-      </c>
-      <c r="C298" t="n">
         <v>9.075025</v>
       </c>
     </row>
@@ -3640,9 +2743,6 @@
         <v>39722</v>
       </c>
       <c r="B299" t="n">
-        <v>0.763349932705249</v>
-      </c>
-      <c r="C299" t="n">
         <v>9.65003230148048</v>
       </c>
     </row>
@@ -3651,9 +2751,6 @@
         <v>39753</v>
       </c>
       <c r="B300" t="n">
-        <v>0.633994444444444</v>
-      </c>
-      <c r="C300" t="n">
         <v>8.37122222222222</v>
       </c>
     </row>
@@ -3662,9 +2759,6 @@
         <v>39783</v>
       </c>
       <c r="B301" t="n">
-        <v>0.488037634408602</v>
-      </c>
-      <c r="C301" t="n">
         <v>7.17379435483871</v>
       </c>
     </row>
@@ -3673,9 +2767,6 @@
         <v>39814</v>
       </c>
       <c r="B302" t="n">
-        <v>0.416387096774194</v>
-      </c>
-      <c r="C302" t="n">
         <v>6.59750403225806</v>
       </c>
     </row>
@@ -3684,9 +2775,6 @@
         <v>39845</v>
       </c>
       <c r="B303" t="n">
-        <v>0.299171130952381</v>
-      </c>
-      <c r="C303" t="n">
         <v>5.64035416666667</v>
       </c>
     </row>
@@ -3695,9 +2783,6 @@
         <v>39873</v>
       </c>
       <c r="B304" t="n">
-        <v>0.270221774193548</v>
-      </c>
-      <c r="C304" t="n">
         <v>5.47724731182796</v>
       </c>
     </row>
@@ -3706,9 +2791,6 @@
         <v>39904</v>
       </c>
       <c r="B305" t="n">
-        <v>0.163576388888889</v>
-      </c>
-      <c r="C305" t="n">
         <v>4.36740972222222</v>
       </c>
     </row>
@@ -3717,9 +2799,6 @@
         <v>39934</v>
       </c>
       <c r="B306" t="n">
-        <v>0.232383064516129</v>
-      </c>
-      <c r="C306" t="n">
         <v>5.07650134408602</v>
       </c>
     </row>
@@ -3728,9 +2807,6 @@
         <v>39965</v>
       </c>
       <c r="B307" t="n">
-        <v>0.464133333333333</v>
-      </c>
-      <c r="C307" t="n">
         <v>6.93794305555556</v>
       </c>
     </row>
@@ -3739,9 +2815,6 @@
         <v>39995</v>
       </c>
       <c r="B308" t="n">
-        <v>0.52880376344086</v>
-      </c>
-      <c r="C308" t="n">
         <v>7.36558333333333</v>
       </c>
     </row>
@@ -3750,9 +2823,6 @@
         <v>40026</v>
       </c>
       <c r="B309" t="n">
-        <v>0.597012096774194</v>
-      </c>
-      <c r="C309" t="n">
         <v>7.94312768817204</v>
       </c>
     </row>
@@ -3761,9 +2831,6 @@
         <v>40057</v>
       </c>
       <c r="B310" t="n">
-        <v>0.6315625</v>
-      </c>
-      <c r="C310" t="n">
         <v>8.22181805555556</v>
       </c>
     </row>
@@ -3772,9 +2839,6 @@
         <v>40087</v>
       </c>
       <c r="B311" t="n">
-        <v>0.552205921938089</v>
-      </c>
-      <c r="C311" t="n">
         <v>7.69838088829071</v>
       </c>
     </row>
@@ -3783,9 +2847,6 @@
         <v>40118</v>
       </c>
       <c r="B312" t="n">
-        <v>0.646330555555556</v>
-      </c>
-      <c r="C312" t="n">
         <v>8.47885138888889</v>
       </c>
     </row>
@@ -3794,9 +2855,6 @@
         <v>40148</v>
       </c>
       <c r="B313" t="n">
-        <v>0.540057795698925</v>
-      </c>
-      <c r="C313" t="n">
         <v>7.5385564516129</v>
       </c>
     </row>
@@ -3805,9 +2863,6 @@
         <v>40179</v>
       </c>
       <c r="B314" t="n">
-        <v>0.374286290322581</v>
-      </c>
-      <c r="C314" t="n">
         <v>6.26761827956989</v>
       </c>
     </row>
@@ -3816,9 +2871,6 @@
         <v>40210</v>
       </c>
       <c r="B315" t="n">
-        <v>0.466458333333333</v>
-      </c>
-      <c r="C315" t="n">
         <v>6.95131398809524</v>
       </c>
     </row>
@@ -3827,9 +2879,6 @@
         <v>40238</v>
       </c>
       <c r="B316" t="n">
-        <v>0.34254435483871</v>
-      </c>
-      <c r="C316" t="n">
         <v>6.01254301075269</v>
       </c>
     </row>
@@ -3838,9 +2887,6 @@
         <v>40269</v>
       </c>
       <c r="B317" t="n">
-        <v>0.393479166666667</v>
-      </c>
-      <c r="C317" t="n">
         <v>6.36629861111111</v>
       </c>
     </row>
@@ -3849,9 +2895,6 @@
         <v>40299</v>
       </c>
       <c r="B318" t="n">
-        <v>0.418784946236559</v>
-      </c>
-      <c r="C318" t="n">
         <v>6.56434543010753</v>
       </c>
     </row>
@@ -3860,9 +2903,6 @@
         <v>40330</v>
       </c>
       <c r="B319" t="n">
-        <v>0.536979166666667</v>
-      </c>
-      <c r="C319" t="n">
         <v>7.47318472222222</v>
       </c>
     </row>
@@ -3871,9 +2911,6 @@
         <v>40360</v>
       </c>
       <c r="B320" t="n">
-        <v>0.676125</v>
-      </c>
-      <c r="C320" t="n">
         <v>8.62068817204301</v>
       </c>
     </row>
@@ -3882,9 +2919,6 @@
         <v>40391</v>
       </c>
       <c r="B321" t="n">
-        <v>0.728245967741936</v>
-      </c>
-      <c r="C321" t="n">
         <v>9.08053897849462</v>
       </c>
     </row>
@@ -3893,9 +2927,6 @@
         <v>40422</v>
       </c>
       <c r="B322" t="n">
-        <v>0.756798611111111</v>
-      </c>
-      <c r="C322" t="n">
         <v>9.36754583333333</v>
       </c>
     </row>
@@ -3904,9 +2935,6 @@
         <v>40452</v>
       </c>
       <c r="B323" t="n">
-        <v>0.537312247644684</v>
-      </c>
-      <c r="C323" t="n">
         <v>7.57660296096904</v>
       </c>
     </row>
@@ -3915,9 +2943,6 @@
         <v>40483</v>
       </c>
       <c r="B324" t="n">
-        <v>0.574725</v>
-      </c>
-      <c r="C324" t="n">
         <v>7.88666805555556</v>
       </c>
     </row>
@@ -3926,9 +2951,6 @@
         <v>40513</v>
       </c>
       <c r="B325" t="n">
-        <v>0.428283602150538</v>
-      </c>
-      <c r="C325" t="n">
         <v>6.62337634408602</v>
       </c>
     </row>
@@ -3937,9 +2959,6 @@
         <v>40544</v>
       </c>
       <c r="B326" t="n">
-        <v>0.32722311827957</v>
-      </c>
-      <c r="C326" t="n">
         <v>5.81785215053763</v>
       </c>
     </row>
@@ -3948,9 +2967,6 @@
         <v>40575</v>
       </c>
       <c r="B327" t="n">
-        <v>0.32328125</v>
-      </c>
-      <c r="C327" t="n">
         <v>5.81339880952381</v>
       </c>
     </row>
@@ -3959,9 +2975,6 @@
         <v>40603</v>
       </c>
       <c r="B328" t="n">
-        <v>0.281556451612903</v>
-      </c>
-      <c r="C328" t="n">
         <v>5.51304569892473</v>
       </c>
     </row>
@@ -3970,9 +2983,6 @@
         <v>40634</v>
       </c>
       <c r="B329" t="n">
-        <v>0.329305555555556</v>
-      </c>
-      <c r="C329" t="n">
         <v>5.90515972222222</v>
       </c>
     </row>
@@ -3981,9 +2991,6 @@
         <v>40664</v>
       </c>
       <c r="B330" t="n">
-        <v>0.448908602150538</v>
-      </c>
-      <c r="C330" t="n">
         <v>6.8056061827957</v>
       </c>
     </row>
@@ -3992,9 +2999,6 @@
         <v>40695</v>
       </c>
       <c r="B331" t="n">
-        <v>0.510933333333333</v>
-      </c>
-      <c r="C331" t="n">
         <v>7.28632361111111</v>
       </c>
     </row>
@@ -4003,9 +3007,6 @@
         <v>40725</v>
       </c>
       <c r="B332" t="n">
-        <v>0.596663978494624</v>
-      </c>
-      <c r="C332" t="n">
         <v>8.00878225806452</v>
       </c>
     </row>
@@ -4014,9 +3015,6 @@
         <v>40756</v>
       </c>
       <c r="B333" t="n">
-        <v>0.644650537634409</v>
-      </c>
-      <c r="C333" t="n">
         <v>8.32841935483871</v>
       </c>
     </row>
@@ -4025,9 +3023,6 @@
         <v>40787</v>
       </c>
       <c r="B334" t="n">
-        <v>0.768270833333333</v>
-      </c>
-      <c r="C334" t="n">
         <v>9.54381111111111</v>
       </c>
     </row>
@@ -4036,9 +3031,6 @@
         <v>40817</v>
       </c>
       <c r="B335" t="n">
-        <v>0.5704266487214</v>
-      </c>
-      <c r="C335" t="n">
         <v>7.83010632570659</v>
       </c>
     </row>
@@ -4047,9 +3039,6 @@
         <v>40848</v>
       </c>
       <c r="B336" t="n">
-        <v>0.626630555555556</v>
-      </c>
-      <c r="C336" t="n">
         <v>8.27813333333333</v>
       </c>
     </row>
@@ -4058,9 +3047,6 @@
         <v>40878</v>
       </c>
       <c r="B337" t="n">
-        <v>0.606317204301075</v>
-      </c>
-      <c r="C337" t="n">
         <v>8.14352956989247</v>
       </c>
     </row>
@@ -4069,9 +3055,6 @@
         <v>40909</v>
       </c>
       <c r="B338" t="n">
-        <v>0.548557795698925</v>
-      </c>
-      <c r="C338" t="n">
         <v>7.67922311827957</v>
       </c>
     </row>
@@ -4080,9 +3063,6 @@
         <v>40940</v>
       </c>
       <c r="B339" t="n">
-        <v>0.506584770114943</v>
-      </c>
-      <c r="C339" t="n">
         <v>7.30959482758621</v>
       </c>
     </row>
@@ -4091,9 +3071,6 @@
         <v>40969</v>
       </c>
       <c r="B340" t="n">
-        <v>0.488018817204301</v>
-      </c>
-      <c r="C340" t="n">
         <v>7.12869086021505</v>
       </c>
     </row>
@@ -4102,9 +3079,6 @@
         <v>41000</v>
       </c>
       <c r="B341" t="n">
-        <v>0.448826388888889</v>
-      </c>
-      <c r="C341" t="n">
         <v>6.81499027777778</v>
       </c>
     </row>
@@ -4113,9 +3087,6 @@
         <v>41030</v>
       </c>
       <c r="B342" t="n">
-        <v>0.53855376344086</v>
-      </c>
-      <c r="C342" t="n">
         <v>7.51104569892473</v>
       </c>
     </row>
@@ -4124,9 +3095,6 @@
         <v>41061</v>
       </c>
       <c r="B343" t="n">
-        <v>0.573961111111111</v>
-      </c>
-      <c r="C343" t="n">
         <v>7.7484875</v>
       </c>
     </row>
@@ -4135,9 +3103,6 @@
         <v>41091</v>
       </c>
       <c r="B344" t="n">
-        <v>0.662662634408602</v>
-      </c>
-      <c r="C344" t="n">
         <v>8.43233467741936</v>
       </c>
     </row>
@@ -4146,9 +3111,6 @@
         <v>41122</v>
       </c>
       <c r="B345" t="n">
-        <v>0.745131720430108</v>
-      </c>
-      <c r="C345" t="n">
         <v>9.28229032258064</v>
       </c>
     </row>
@@ -4157,9 +3119,6 @@
         <v>41153</v>
       </c>
       <c r="B346" t="n">
-        <v>0.745563888888889</v>
-      </c>
-      <c r="C346" t="n">
         <v>9.29357083333333</v>
       </c>
     </row>
@@ -4168,9 +3127,6 @@
         <v>41183</v>
       </c>
       <c r="B347" t="n">
-        <v>0.708402422611036</v>
-      </c>
-      <c r="C347" t="n">
         <v>9.10793135935397</v>
       </c>
     </row>
@@ -4179,9 +3135,6 @@
         <v>41214</v>
       </c>
       <c r="B348" t="n">
-        <v>0.556672222222222</v>
-      </c>
-      <c r="C348" t="n">
         <v>7.79424583333333</v>
       </c>
     </row>
@@ -4190,9 +3143,6 @@
         <v>41244</v>
       </c>
       <c r="B349" t="n">
-        <v>0.528204301075269</v>
-      </c>
-      <c r="C349" t="n">
         <v>7.5452311827957</v>
       </c>
     </row>
@@ -4201,9 +3151,6 @@
         <v>41275</v>
       </c>
       <c r="B350" t="n">
-        <v>0.484350806451613</v>
-      </c>
-      <c r="C350" t="n">
         <v>7.15845161290323</v>
       </c>
     </row>
@@ -4212,9 +3159,6 @@
         <v>41306</v>
       </c>
       <c r="B351" t="n">
-        <v>0.569654761904762</v>
-      </c>
-      <c r="C351" t="n">
         <v>7.82476041666667</v>
       </c>
     </row>
@@ -4223,9 +3167,6 @@
         <v>41334</v>
       </c>
       <c r="B352" t="n">
-        <v>0.413784946236559</v>
-      </c>
-      <c r="C352" t="n">
         <v>6.53585215053763</v>
       </c>
     </row>
@@ -4234,9 +3175,6 @@
         <v>41365</v>
       </c>
       <c r="B353" t="n">
-        <v>0.337830555555556</v>
-      </c>
-      <c r="C353" t="n">
         <v>5.90905972222222</v>
       </c>
     </row>
@@ -4245,9 +3183,6 @@
         <v>41395</v>
       </c>
       <c r="B354" t="n">
-        <v>0.427146505376344</v>
-      </c>
-      <c r="C354" t="n">
         <v>6.63238306451613</v>
       </c>
     </row>
@@ -4256,9 +3191,6 @@
         <v>41426</v>
       </c>
       <c r="B355" t="n">
-        <v>0.498765277777778</v>
-      </c>
-      <c r="C355" t="n">
         <v>7.20654305555556</v>
       </c>
     </row>
@@ -4267,9 +3199,6 @@
         <v>41456</v>
       </c>
       <c r="B356" t="n">
-        <v>0.55880376344086</v>
-      </c>
-      <c r="C356" t="n">
         <v>7.67144623655914</v>
       </c>
     </row>
@@ -4278,9 +3207,6 @@
         <v>41487</v>
       </c>
       <c r="B357" t="n">
-        <v>0.683047043010753</v>
-      </c>
-      <c r="C357" t="n">
         <v>8.63764650537634</v>
       </c>
     </row>
@@ -4289,9 +3215,6 @@
         <v>41518</v>
       </c>
       <c r="B358" t="n">
-        <v>0.719705555555556</v>
-      </c>
-      <c r="C358" t="n">
         <v>9.06252638888889</v>
       </c>
     </row>
@@ -4300,9 +3223,6 @@
         <v>41548</v>
       </c>
       <c r="B359" t="n">
-        <v>0.681557200538358</v>
-      </c>
-      <c r="C359" t="n">
         <v>8.8183001345895</v>
       </c>
     </row>
@@ -4311,9 +3231,6 @@
         <v>41579</v>
       </c>
       <c r="B360" t="n">
-        <v>0.611115277777778</v>
-      </c>
-      <c r="C360" t="n">
         <v>8.12240555555556</v>
       </c>
     </row>
@@ -4322,9 +3239,6 @@
         <v>41609</v>
       </c>
       <c r="B361" t="n">
-        <v>0.51109811827957</v>
-      </c>
-      <c r="C361" t="n">
         <v>7.34573252688172</v>
       </c>
     </row>
@@ -4333,9 +3247,6 @@
         <v>41640</v>
       </c>
       <c r="B362" t="n">
-        <v>0.551360215053763</v>
-      </c>
-      <c r="C362" t="n">
         <v>7.63974327956989</v>
       </c>
     </row>
@@ -4344,9 +3255,6 @@
         <v>41671</v>
       </c>
       <c r="B363" t="n">
-        <v>0.425958333333333</v>
-      </c>
-      <c r="C363" t="n">
         <v>6.64207142857143</v>
       </c>
     </row>
@@ -4355,9 +3263,6 @@
         <v>41699</v>
       </c>
       <c r="B364" t="n">
-        <v>0.358967741935484</v>
-      </c>
-      <c r="C364" t="n">
         <v>6.15806586021505</v>
       </c>
     </row>
@@ -4366,9 +3271,6 @@
         <v>41730</v>
       </c>
       <c r="B365" t="n">
-        <v>0.296570833333333</v>
-      </c>
-      <c r="C365" t="n">
         <v>5.60487777777778</v>
       </c>
     </row>
@@ -4377,9 +3279,6 @@
         <v>41760</v>
       </c>
       <c r="B366" t="n">
-        <v>0.417220430107527</v>
-      </c>
-      <c r="C366" t="n">
         <v>6.55802553763441</v>
       </c>
     </row>
@@ -4388,9 +3287,6 @@
         <v>41791</v>
       </c>
       <c r="B367" t="n">
-        <v>0.595927777777778</v>
-      </c>
-      <c r="C367" t="n">
         <v>7.92063055555556</v>
       </c>
     </row>
@@ -4399,9 +3295,6 @@
         <v>41821</v>
       </c>
       <c r="B368" t="n">
-        <v>0.647840053763441</v>
-      </c>
-      <c r="C368" t="n">
         <v>8.35090053763441</v>
       </c>
     </row>
@@ -4410,9 +3303,6 @@
         <v>41852</v>
       </c>
       <c r="B369" t="n">
-        <v>0.686383064516129</v>
-      </c>
-      <c r="C369" t="n">
         <v>8.64308467741935</v>
       </c>
     </row>
@@ -4421,9 +3311,6 @@
         <v>41883</v>
       </c>
       <c r="B370" t="n">
-        <v>0.677109722222222</v>
-      </c>
-      <c r="C370" t="n">
         <v>8.68135972222222</v>
       </c>
     </row>
@@ -4432,9 +3319,6 @@
         <v>41913</v>
       </c>
       <c r="B371" t="n">
-        <v>0.73106864064603</v>
-      </c>
-      <c r="C371" t="n">
         <v>9.18369044414536</v>
       </c>
     </row>
@@ -4443,9 +3327,6 @@
         <v>41944</v>
       </c>
       <c r="B372" t="n">
-        <v>0.559073611111111</v>
-      </c>
-      <c r="C372" t="n">
         <v>7.78409861111111</v>
       </c>
     </row>
@@ -4454,9 +3335,6 @@
         <v>41974</v>
       </c>
       <c r="B373" t="n">
-        <v>0.618895161290323</v>
-      </c>
-      <c r="C373" t="n">
         <v>8.17390322580645</v>
       </c>
     </row>
@@ -4465,9 +3343,6 @@
         <v>42005</v>
       </c>
       <c r="B374" t="n">
-        <v>0.579486559139785</v>
-      </c>
-      <c r="C374" t="n">
         <v>7.84776209677419</v>
       </c>
     </row>
@@ -4476,9 +3351,6 @@
         <v>42036</v>
       </c>
       <c r="B375" t="n">
-        <v>0.437294642857143</v>
-      </c>
-      <c r="C375" t="n">
         <v>6.6930505952381</v>
       </c>
     </row>
@@ -4487,9 +3359,6 @@
         <v>42064</v>
       </c>
       <c r="B376" t="n">
-        <v>0.369793010752688</v>
-      </c>
-      <c r="C376" t="n">
         <v>6.22195430107527</v>
       </c>
     </row>
@@ -4498,9 +3367,6 @@
         <v>42095</v>
       </c>
       <c r="B377" t="n">
-        <v>0.3319625</v>
-      </c>
-      <c r="C377" t="n">
         <v>5.90935833333333</v>
       </c>
     </row>
@@ -4509,9 +3375,6 @@
         <v>42125</v>
       </c>
       <c r="B378" t="n">
-        <v>0.495021505376344</v>
-      </c>
-      <c r="C378" t="n">
         <v>7.18063844086022</v>
       </c>
     </row>
@@ -4520,9 +3383,6 @@
         <v>42156</v>
       </c>
       <c r="B379" t="n">
-        <v>0.570070833333333</v>
-      </c>
-      <c r="C379" t="n">
         <v>7.74636111111111</v>
       </c>
     </row>
@@ -4531,9 +3391,6 @@
         <v>42186</v>
       </c>
       <c r="B380" t="n">
-        <v>0.640474462365591</v>
-      </c>
-      <c r="C380" t="n">
         <v>8.37867607526882</v>
       </c>
     </row>
@@ -4542,9 +3399,6 @@
         <v>42217</v>
       </c>
       <c r="B381" t="n">
-        <v>0.715611559139785</v>
-      </c>
-      <c r="C381" t="n">
         <v>9.01402016129032</v>
       </c>
     </row>
@@ -4553,9 +3407,6 @@
         <v>42248</v>
       </c>
       <c r="B382" t="n">
-        <v>0.655891666666667</v>
-      </c>
-      <c r="C382" t="n">
         <v>8.5494625</v>
       </c>
     </row>
@@ -4564,9 +3415,6 @@
         <v>42278</v>
       </c>
       <c r="B383" t="n">
-        <v>0.667226110363392</v>
-      </c>
-      <c r="C383" t="n">
         <v>8.77404576043069</v>
       </c>
     </row>
@@ -4575,9 +3423,6 @@
         <v>42309</v>
       </c>
       <c r="B384" t="n">
-        <v>0.589205555555556</v>
-      </c>
-      <c r="C384" t="n">
         <v>8.05685555555556</v>
       </c>
     </row>
@@ -4586,9 +3431,6 @@
         <v>42339</v>
       </c>
       <c r="B385" t="n">
-        <v>0.57747311827957</v>
-      </c>
-      <c r="C385" t="n">
         <v>7.86585887096774</v>
       </c>
     </row>
@@ -4597,9 +3439,6 @@
         <v>42370</v>
       </c>
       <c r="B386" t="n">
-        <v>0.352334677419355</v>
-      </c>
-      <c r="C386" t="n">
         <v>6.12247983870968</v>
       </c>
     </row>
@@ -4608,9 +3447,6 @@
         <v>42401</v>
       </c>
       <c r="B387" t="n">
-        <v>0.475406609195402</v>
-      </c>
-      <c r="C387" t="n">
         <v>7.02203017241379</v>
       </c>
     </row>
@@ -4619,9 +3455,6 @@
         <v>42430</v>
       </c>
       <c r="B388" t="n">
-        <v>0.400065860215054</v>
-      </c>
-      <c r="C388" t="n">
         <v>6.47105376344086</v>
       </c>
     </row>
@@ -4630,9 +3463,6 @@
         <v>42461</v>
       </c>
       <c r="B389" t="n">
-        <v>0.506443055555556</v>
-      </c>
-      <c r="C389" t="n">
         <v>7.22172638888889</v>
       </c>
     </row>
@@ -4641,9 +3471,6 @@
         <v>42491</v>
       </c>
       <c r="B390" t="n">
-        <v>0.452700268817204</v>
-      </c>
-      <c r="C390" t="n">
         <v>6.86861693548387</v>
       </c>
     </row>
@@ -4652,9 +3479,6 @@
         <v>42522</v>
       </c>
       <c r="B391" t="n">
-        <v>0.547847222222222</v>
-      </c>
-      <c r="C391" t="n">
         <v>7.57594583333333</v>
       </c>
     </row>
@@ -4663,9 +3487,6 @@
         <v>42552</v>
       </c>
       <c r="B392" t="n">
-        <v>0.656172043010753</v>
-      </c>
-      <c r="C392" t="n">
         <v>8.48725806451613</v>
       </c>
     </row>
@@ -4674,9 +3495,6 @@
         <v>42583</v>
       </c>
       <c r="B393" t="n">
-        <v>0.657834677419355</v>
-      </c>
-      <c r="C393" t="n">
         <v>8.52921505376344</v>
       </c>
     </row>
@@ -4685,9 +3503,6 @@
         <v>42614</v>
       </c>
       <c r="B394" t="n">
-        <v>0.681329166666667</v>
-      </c>
-      <c r="C394" t="n">
         <v>8.85300555555555</v>
       </c>
     </row>
@@ -4696,9 +3511,6 @@
         <v>42644</v>
       </c>
       <c r="B395" t="n">
-        <v>0.716851951547779</v>
-      </c>
-      <c r="C395" t="n">
         <v>9.1931601615074</v>
       </c>
     </row>
@@ -4707,9 +3519,6 @@
         <v>42675</v>
       </c>
       <c r="B396" t="n">
-        <v>0.6847</v>
-      </c>
-      <c r="C396" t="n">
         <v>8.90000694444444</v>
       </c>
     </row>
@@ -4718,9 +3527,6 @@
         <v>42705</v>
       </c>
       <c r="B397" t="n">
-        <v>0.621697580645161</v>
-      </c>
-      <c r="C397" t="n">
         <v>8.24515322580645</v>
       </c>
     </row>
@@ -4729,9 +3535,6 @@
         <v>42736</v>
       </c>
       <c r="B398" t="n">
-        <v>0.518666666666667</v>
-      </c>
-      <c r="C398" t="n">
         <v>7.37132123655914</v>
       </c>
     </row>
@@ -4740,9 +3543,6 @@
         <v>42767</v>
       </c>
       <c r="B399" t="n">
-        <v>0.404785714285714</v>
-      </c>
-      <c r="C399" t="n">
         <v>6.48120238095238</v>
       </c>
     </row>
@@ -4751,9 +3551,6 @@
         <v>42795</v>
       </c>
       <c r="B400" t="n">
-        <v>0.286700268817204</v>
-      </c>
-      <c r="C400" t="n">
         <v>5.601875</v>
       </c>
     </row>
@@ -4762,9 +3559,6 @@
         <v>42826</v>
       </c>
       <c r="B401" t="n">
-        <v>0.390869444444444</v>
-      </c>
-      <c r="C401" t="n">
         <v>6.37255416666667</v>
       </c>
     </row>
@@ -4773,9 +3567,6 @@
         <v>42856</v>
       </c>
       <c r="B402" t="n">
-        <v>0.42802688172043</v>
-      </c>
-      <c r="C402" t="n">
         <v>6.66866801075269</v>
       </c>
     </row>
@@ -4784,9 +3575,6 @@
         <v>42887</v>
       </c>
       <c r="B403" t="n">
-        <v>0.595376388888889</v>
-      </c>
-      <c r="C403" t="n">
         <v>7.97629444444444</v>
       </c>
     </row>
@@ -4795,9 +3583,6 @@
         <v>42917</v>
       </c>
       <c r="B404" t="n">
-        <v>0.752860215053763</v>
-      </c>
-      <c r="C404" t="n">
         <v>9.50362365591398</v>
       </c>
     </row>
@@ -4806,9 +3591,6 @@
         <v>42948</v>
       </c>
       <c r="B405" t="n">
-        <v>0.667717741935484</v>
-      </c>
-      <c r="C405" t="n">
         <v>8.54665053763441</v>
       </c>
     </row>
@@ -4817,9 +3599,6 @@
         <v>42979</v>
       </c>
       <c r="B406" t="n">
-        <v>0.817465277777778</v>
-      </c>
-      <c r="C406" t="n">
         <v>10.0745930555556</v>
       </c>
     </row>
@@ -4828,9 +3607,6 @@
         <v>43009</v>
       </c>
       <c r="B407" t="n">
-        <v>0.732932705248991</v>
-      </c>
-      <c r="C407" t="n">
         <v>9.34792866756393</v>
       </c>
     </row>
@@ -4839,9 +3615,6 @@
         <v>43040</v>
       </c>
       <c r="B408" t="n">
-        <v>0.598695833333333</v>
-      </c>
-      <c r="C408" t="n">
         <v>8.13466111111111</v>
       </c>
     </row>
@@ -4850,9 +3623,6 @@
         <v>43070</v>
       </c>
       <c r="B409" t="n">
-        <v>0.590719086021505</v>
-      </c>
-      <c r="C409" t="n">
         <v>7.96248387096774</v>
       </c>
     </row>
@@ -4861,9 +3631,6 @@
         <v>43101</v>
       </c>
       <c r="B410" t="n">
-        <v>0.492186827956989</v>
-      </c>
-      <c r="C410" t="n">
         <v>7.19162096774194</v>
       </c>
     </row>
@@ -4872,9 +3639,6 @@
         <v>43132</v>
       </c>
       <c r="B411" t="n">
-        <v>0.360508928571429</v>
-      </c>
-      <c r="C411" t="n">
         <v>6.12417410714286</v>
       </c>
     </row>
@@ -4883,9 +3647,6 @@
         <v>43160</v>
       </c>
       <c r="B412" t="n">
-        <v>0.331995967741935</v>
-      </c>
-      <c r="C412" t="n">
         <v>5.95437634408602</v>
       </c>
     </row>
@@ -4894,9 +3655,6 @@
         <v>43191</v>
       </c>
       <c r="B413" t="n">
-        <v>0.340690277777778</v>
-      </c>
-      <c r="C413" t="n">
         <v>5.95169027777778</v>
       </c>
     </row>
@@ -4905,9 +3663,6 @@
         <v>43221</v>
       </c>
       <c r="B414" t="n">
-        <v>0.487918010752688</v>
-      </c>
-      <c r="C414" t="n">
         <v>7.11543817204301</v>
       </c>
     </row>
@@ -4916,9 +3671,6 @@
         <v>43252</v>
       </c>
       <c r="B415" t="n">
-        <v>0.61385</v>
-      </c>
-      <c r="C415" t="n">
         <v>8.04417361111111</v>
       </c>
     </row>
@@ -4927,9 +3679,6 @@
         <v>43282</v>
       </c>
       <c r="B416" t="n">
-        <v>0.649145161290323</v>
-      </c>
-      <c r="C416" t="n">
         <v>8.33500940860215</v>
       </c>
     </row>
@@ -4938,9 +3687,6 @@
         <v>43313</v>
       </c>
       <c r="B417" t="n">
-        <v>0.646623655913979</v>
-      </c>
-      <c r="C417" t="n">
         <v>8.41782930107527</v>
       </c>
     </row>
@@ -4949,9 +3695,6 @@
         <v>43344</v>
       </c>
       <c r="B418" t="n">
-        <v>0.727255555555556</v>
-      </c>
-      <c r="C418" t="n">
         <v>9.15843888888889</v>
       </c>
     </row>
@@ -4960,9 +3703,6 @@
         <v>43374</v>
       </c>
       <c r="B419" t="n">
-        <v>0.593493279569893</v>
-      </c>
-      <c r="C419" t="n">
         <v>8.0906747311828</v>
       </c>
     </row>
@@ -4971,9 +3711,6 @@
         <v>43405</v>
       </c>
       <c r="B420" t="n">
-        <v>0.68692628650904</v>
-      </c>
-      <c r="C420" t="n">
         <v>8.845280945758</v>
       </c>
     </row>
@@ -4982,9 +3719,6 @@
         <v>43435</v>
       </c>
       <c r="B421" t="n">
-        <v>0.477509408602151</v>
-      </c>
-      <c r="C421" t="n">
         <v>7.06432661290323</v>
       </c>
     </row>
@@ -4993,9 +3727,6 @@
         <v>43466</v>
       </c>
       <c r="B422" t="n">
-        <v>0.445450268817204</v>
-      </c>
-      <c r="C422" t="n">
         <v>6.77799462365591</v>
       </c>
     </row>
@@ -5004,9 +3735,6 @@
         <v>43497</v>
       </c>
       <c r="B423" t="n">
-        <v>0.319877976190476</v>
-      </c>
-      <c r="C423" t="n">
         <v>5.75557440476191</v>
       </c>
     </row>
@@ -5015,9 +3743,6 @@
         <v>43525</v>
       </c>
       <c r="B424" t="n">
-        <v>0.307577956989247</v>
-      </c>
-      <c r="C424" t="n">
         <v>5.74503091397849</v>
       </c>
     </row>
@@ -5026,9 +3751,6 @@
         <v>43556</v>
       </c>
       <c r="B425" t="n">
-        <v>0.274766666666667</v>
-      </c>
-      <c r="C425" t="n">
         <v>5.48417222222222</v>
       </c>
     </row>
@@ -5037,9 +3759,6 @@
         <v>43586</v>
       </c>
       <c r="B426" t="n">
-        <v>0.421447580645161</v>
-      </c>
-      <c r="C426" t="n">
         <v>6.58857392473118</v>
       </c>
     </row>
@@ -5048,9 +3767,6 @@
         <v>43617</v>
       </c>
       <c r="B427" t="n">
-        <v>0.585544444444444</v>
-      </c>
-      <c r="C427" t="n">
         <v>7.87532777777778</v>
       </c>
     </row>
@@ -5059,9 +3775,6 @@
         <v>43647</v>
       </c>
       <c r="B428" t="n">
-        <v>0.557430107526882</v>
-      </c>
-      <c r="C428" t="n">
         <v>7.65848521505376</v>
       </c>
     </row>
@@ -5070,9 +3783,6 @@
         <v>43678</v>
       </c>
       <c r="B429" t="n">
-        <v>0.710240591397849</v>
-      </c>
-      <c r="C429" t="n">
         <v>8.93884811827957</v>
       </c>
     </row>
@@ -5081,9 +3791,6 @@
         <v>43709</v>
       </c>
       <c r="B430" t="n">
-        <v>0.691122222222222</v>
-      </c>
-      <c r="C430" t="n">
         <v>8.874975</v>
       </c>
     </row>
@@ -5092,9 +3799,6 @@
         <v>43739</v>
       </c>
       <c r="B431" t="n">
-        <v>0.666979838709677</v>
-      </c>
-      <c r="C431" t="n">
         <v>8.8005685483871</v>
       </c>
     </row>
@@ -5103,9 +3807,6 @@
         <v>43770</v>
       </c>
       <c r="B432" t="n">
-        <v>0.573636111111111</v>
-      </c>
-      <c r="C432" t="n">
         <v>7.92070416666667</v>
       </c>
     </row>
@@ -5114,9 +3815,6 @@
         <v>43800</v>
       </c>
       <c r="B433" t="n">
-        <v>0.525494623655914</v>
-      </c>
-      <c r="C433" t="n">
         <v>7.49483064516129</v>
       </c>
     </row>
@@ -5125,9 +3823,6 @@
         <v>43831</v>
       </c>
       <c r="B434" t="n">
-        <v>0.335461021505376</v>
-      </c>
-      <c r="C434" t="n">
         <v>5.90918010752688</v>
       </c>
     </row>
@@ -5136,9 +3831,6 @@
         <v>43862</v>
       </c>
       <c r="B435" t="n">
-        <v>0.279061781609195</v>
-      </c>
-      <c r="C435" t="n">
         <v>5.51534770114942</v>
       </c>
     </row>
@@ -5147,9 +3839,6 @@
         <v>43891</v>
       </c>
       <c r="B436" t="n">
-        <v>0.182522849462366</v>
-      </c>
-      <c r="C436" t="n">
         <v>4.58324193548387</v>
       </c>
     </row>
@@ -5158,9 +3847,6 @@
         <v>43922</v>
       </c>
       <c r="B437" t="n">
-        <v>0.269497222222222</v>
-      </c>
-      <c r="C437" t="n">
         <v>5.4573375</v>
       </c>
     </row>
@@ -5169,9 +3855,6 @@
         <v>43952</v>
       </c>
       <c r="B438" t="n">
-        <v>0.389720430107527</v>
-      </c>
-      <c r="C438" t="n">
         <v>6.35122311827957</v>
       </c>
     </row>
@@ -5180,9 +3863,6 @@
         <v>43983</v>
       </c>
       <c r="B439" t="n">
-        <v>0.553669444444444</v>
-      </c>
-      <c r="C439" t="n">
         <v>7.65281111111111</v>
       </c>
     </row>
@@ -5191,9 +3871,6 @@
         <v>44013</v>
       </c>
       <c r="B440" t="n">
-        <v>0.59982123655914</v>
-      </c>
-      <c r="C440" t="n">
         <v>7.95877553763441</v>
       </c>
     </row>
@@ -5202,9 +3879,6 @@
         <v>44044</v>
       </c>
       <c r="B441" t="n">
-        <v>0.662420698924731</v>
-      </c>
-      <c r="C441" t="n">
         <v>8.56799193548387</v>
       </c>
     </row>
@@ -5213,9 +3887,6 @@
         <v>44075</v>
       </c>
       <c r="B442" t="n">
-        <v>0.643261111111111</v>
-      </c>
-      <c r="C442" t="n">
         <v>8.44869861111111</v>
       </c>
     </row>
@@ -5224,9 +3895,6 @@
         <v>44105</v>
       </c>
       <c r="B443" t="n">
-        <v>0.623033602150538</v>
-      </c>
-      <c r="C443" t="n">
         <v>8.32545430107527</v>
       </c>
     </row>
@@ -5235,9 +3903,6 @@
         <v>44136</v>
       </c>
       <c r="B444" t="n">
-        <v>0.5371875</v>
-      </c>
-      <c r="C444" t="n">
         <v>7.54828333333333</v>
       </c>
     </row>
@@ -5246,9 +3911,6 @@
         <v>44166</v>
       </c>
       <c r="B445" t="n">
-        <v>0.540328398384926</v>
-      </c>
-      <c r="C445" t="n">
         <v>7.57568775235532</v>
       </c>
     </row>
@@ -5257,9 +3919,6 @@
         <v>44197</v>
       </c>
       <c r="B446" t="n">
-        <v>0.411592741935484</v>
-      </c>
-      <c r="C446" t="n">
         <v>6.5812002688172</v>
       </c>
     </row>
@@ -5268,9 +3927,6 @@
         <v>44228</v>
       </c>
       <c r="B447" t="n">
-        <v>0.332056547619048</v>
-      </c>
-      <c r="C447" t="n">
         <v>5.89933928571429</v>
       </c>
     </row>
@@ -5279,9 +3935,6 @@
         <v>44256</v>
       </c>
       <c r="B448" t="n">
-        <v>0.323815860215054</v>
-      </c>
-      <c r="C448" t="n">
         <v>5.8627002688172</v>
       </c>
     </row>
@@ -5290,9 +3943,6 @@
         <v>44287</v>
       </c>
       <c r="B449" t="n">
-        <v>0.346191666666667</v>
-      </c>
-      <c r="C449" t="n">
         <v>6.02150694444444</v>
       </c>
     </row>
@@ -5301,9 +3951,6 @@
         <v>44317</v>
       </c>
       <c r="B450" t="n">
-        <v>0.397077956989247</v>
-      </c>
-      <c r="C450" t="n">
         <v>6.40209811827957</v>
       </c>
     </row>
@@ -5312,9 +3959,6 @@
         <v>44348</v>
       </c>
       <c r="B451" t="n">
-        <v>0.428313888888889</v>
-      </c>
-      <c r="C451" t="n">
         <v>6.67687916666667</v>
       </c>
     </row>
@@ -5323,9 +3967,6 @@
         <v>44378</v>
       </c>
       <c r="B452" t="n">
-        <v>0.539043010752688</v>
-      </c>
-      <c r="C452" t="n">
         <v>7.52696908602151</v>
       </c>
     </row>
@@ -5334,9 +3975,6 @@
         <v>44409</v>
       </c>
       <c r="B453" t="n">
-        <v>0.696745967741936</v>
-      </c>
-      <c r="C453" t="n">
         <v>8.81443010752688</v>
       </c>
     </row>
@@ -5345,9 +3983,6 @@
         <v>44440</v>
       </c>
       <c r="B454" t="n">
-        <v>0.636218055555556</v>
-      </c>
-      <c r="C454" t="n">
         <v>8.32030694444444</v>
       </c>
     </row>
@@ -5356,9 +3991,6 @@
         <v>44470</v>
       </c>
       <c r="B455" t="n">
-        <v>0.576139784946237</v>
-      </c>
-      <c r="C455" t="n">
         <v>7.89707661290323</v>
       </c>
     </row>
@@ -5367,9 +3999,6 @@
         <v>44501</v>
       </c>
       <c r="B456" t="n">
-        <v>0.510336111111111</v>
-      </c>
-      <c r="C456" t="n">
         <v>7.41563611111111</v>
       </c>
     </row>
@@ -5378,9 +4007,6 @@
         <v>44531</v>
       </c>
       <c r="B457" t="n">
-        <v>0.507405913978495</v>
-      </c>
-      <c r="C457" t="n">
         <v>7.34944892473118</v>
       </c>
     </row>
@@ -5389,9 +4015,6 @@
         <v>44562</v>
       </c>
       <c r="B458" t="n">
-        <v>0.327087365591398</v>
-      </c>
-      <c r="C458" t="n">
         <v>5.92401075268817</v>
       </c>
     </row>
@@ -5400,9 +4023,6 @@
         <v>44593</v>
       </c>
       <c r="B459" t="n">
-        <v>0.351172619047619</v>
-      </c>
-      <c r="C459" t="n">
         <v>6.04483928571429</v>
       </c>
     </row>
@@ -5411,9 +4031,6 @@
         <v>44621</v>
       </c>
       <c r="B460" t="n">
-        <v>0.306572580645161</v>
-      </c>
-      <c r="C460" t="n">
         <v>5.73883467741936</v>
       </c>
     </row>
@@ -5422,9 +4039,6 @@
         <v>44652</v>
       </c>
       <c r="B461" t="n">
-        <v>0.322173611111111</v>
-      </c>
-      <c r="C461" t="n">
         <v>5.84510555555556</v>
       </c>
     </row>
@@ -5433,9 +4047,6 @@
         <v>44682</v>
       </c>
       <c r="B462" t="n">
-        <v>0.398907258064516</v>
-      </c>
-      <c r="C462" t="n">
         <v>6.46697311827957</v>
       </c>
     </row>
@@ -5444,9 +4055,6 @@
         <v>44713</v>
       </c>
       <c r="B463" t="n">
-        <v>0.419916666666667</v>
-      </c>
-      <c r="C463" t="n">
         <v>6.61412916666667</v>
       </c>
     </row>
@@ -5455,9 +4063,6 @@
         <v>44743</v>
       </c>
       <c r="B464" t="n">
-        <v>0.64364247311828</v>
-      </c>
-      <c r="C464" t="n">
         <v>8.31139650537634</v>
       </c>
     </row>
@@ -5466,9 +4071,6 @@
         <v>44774</v>
       </c>
       <c r="B465" t="n">
-        <v>0.636547043010753</v>
-      </c>
-      <c r="C465" t="n">
         <v>8.30518279569892</v>
       </c>
     </row>
@@ -5477,9 +4079,6 @@
         <v>44805</v>
       </c>
       <c r="B466" t="n">
-        <v>0.596829166666667</v>
-      </c>
-      <c r="C466" t="n">
         <v>8.06769444444445</v>
       </c>
     </row>
@@ -5488,9 +4087,6 @@
         <v>44835</v>
       </c>
       <c r="B467" t="n">
-        <v>0.63267876344086</v>
-      </c>
-      <c r="C467" t="n">
         <v>8.38435483870968</v>
       </c>
     </row>
@@ -5499,9 +4095,6 @@
         <v>44866</v>
       </c>
       <c r="B468" t="n">
-        <v>0.380231944444444</v>
-      </c>
-      <c r="C468" t="n">
         <v>6.24891388888889</v>
       </c>
     </row>
@@ -5510,9 +4103,6 @@
         <v>44896</v>
       </c>
       <c r="B469" t="n">
-        <v>0.437157258064516</v>
-      </c>
-      <c r="C469" t="n">
         <v>6.72358870967742</v>
       </c>
     </row>
@@ -5521,9 +4111,6 @@
         <v>44927</v>
       </c>
       <c r="B470" t="n">
-        <v>0.421170698924731</v>
-      </c>
-      <c r="C470" t="n">
         <v>6.62920833333333</v>
       </c>
     </row>
@@ -5532,9 +4119,6 @@
         <v>44958</v>
       </c>
       <c r="B471" t="n">
-        <v>0.421017857142857</v>
-      </c>
-      <c r="C471" t="n">
         <v>6.6390505952381</v>
       </c>
     </row>
@@ -5543,9 +4127,6 @@
         <v>44986</v>
       </c>
       <c r="B472" t="n">
-        <v>0.319626344086022</v>
-      </c>
-      <c r="C472" t="n">
         <v>5.71390994623656</v>
       </c>
     </row>
@@ -5554,9 +4135,6 @@
         <v>45017</v>
       </c>
       <c r="B473" t="n">
-        <v>0.247488888888889</v>
-      </c>
-      <c r="C473" t="n">
         <v>5.13378888888889</v>
       </c>
     </row>
@@ -5565,9 +4143,6 @@
         <v>45047</v>
       </c>
       <c r="B474" t="n">
-        <v>0.380798387096774</v>
-      </c>
-      <c r="C474" t="n">
         <v>6.27402284946237</v>
       </c>
     </row>
@@ -5576,9 +4151,6 @@
         <v>45078</v>
       </c>
       <c r="B475" t="n">
-        <v>0.535875</v>
-      </c>
-      <c r="C475" t="n">
         <v>7.49782777777778</v>
       </c>
     </row>
@@ -5587,9 +4159,6 @@
         <v>45108</v>
       </c>
       <c r="B476" t="n">
-        <v>0.576997311827957</v>
-      </c>
-      <c r="C476" t="n">
         <v>7.79154166666667</v>
       </c>
     </row>
@@ -5598,9 +4167,6 @@
         <v>45139</v>
       </c>
       <c r="B477" t="n">
-        <v>0.57160752688172</v>
-      </c>
-      <c r="C477" t="n">
         <v>7.75857123655914</v>
       </c>
     </row>
@@ -5609,9 +4175,6 @@
         <v>45170</v>
       </c>
       <c r="B478" t="n">
-        <v>0.680418055555556</v>
-      </c>
-      <c r="C478" t="n">
         <v>8.70347222222222</v>
       </c>
     </row>
@@ -5620,9 +4183,6 @@
         <v>45200</v>
       </c>
       <c r="B479" t="n">
-        <v>0.563541666666667</v>
-      </c>
-      <c r="C479" t="n">
         <v>7.77642607526882</v>
       </c>
     </row>
@@ -5631,9 +4191,6 @@
         <v>45231</v>
       </c>
       <c r="B480" t="n">
-        <v>0.511040277777778</v>
-      </c>
-      <c r="C480" t="n">
         <v>7.38578194444444</v>
       </c>
     </row>
@@ -5642,9 +4199,6 @@
         <v>45261</v>
       </c>
       <c r="B481" t="n">
-        <v>0.47476747311828</v>
-      </c>
-      <c r="C481" t="n">
         <v>7.00970295698925</v>
       </c>
     </row>
